--- a/Kachi_Gun/Table/Mission.xlsx
+++ b/Kachi_Gun/Table/Mission.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>Base_Reward_Gems</t>
+          <t>Base_Reward_Value</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -538,6 +538,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Impl_Status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Max_Tier</t>
         </is>
       </c>
     </row>
@@ -558,10 +563,10 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -573,7 +578,7 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>구현 완료 (Mission.csv)</t>
+          <t>10-20: 1단계 ≈ 1.5챕터 처치 수 (Mission_Tier Kill_Target)</t>
         </is>
       </c>
     </row>
@@ -594,10 +599,10 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -609,8 +614,11 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>구현 완료 (Mission.csv, 750스테이지 맞춤 성장)</t>
-        </is>
+          <t>10-20: 5스테이지마다 1단계, 750(150단계)에서 끝</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -630,10 +638,10 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -666,10 +674,10 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -702,22 +710,22 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>3|10|25|50|100|200|400</t>
+          <t>1|2|4|8|16|32|64</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.15</v>
+        <v>2</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>확장 기획 (총알 드래그 합성 횟수)</t>
+          <t>10-20: 1·2·4·8… (두 배씩)</t>
         </is>
       </c>
     </row>
@@ -796,12 +804,12 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>Reward_Gems</t>
+          <t>Reward_Value (다이아30%+골드70%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cum_Reward_Gems_Per_Mission</t>
+          <t>Cum_Reward_Value_Per_Mission</t>
         </is>
       </c>
     </row>
@@ -810,17 +818,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="7" t="n">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F2" s="5" t="n">
@@ -836,10 +844,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
@@ -847,24 +855,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>3</v>
+        <v>2.003</v>
       </c>
       <c r="D3" s="7" t="n">
-        <v>300</v>
+        <v>677</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F3" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" s="7" t="n">
         <v>10</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>15</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>1</v>
@@ -873,10 +881,10 @@
         <v>2</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -884,24 +892,24 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>2.33</v>
+        <v>1.6248</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>700</v>
+        <v>1100</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1.1k</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <v>15</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>30</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>2</v>
@@ -910,10 +918,10 @@
         <v>4</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
@@ -921,24 +929,24 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>2.86</v>
+        <v>2.2091</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>2000</v>
+        <v>2430</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2k</t>
+          <t>2.43k</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="7" t="n">
         <v>20</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>50</v>
       </c>
       <c r="H5" s="5" t="n">
         <v>2</v>
@@ -947,10 +955,10 @@
         <v>6</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>120</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -958,24 +966,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2.5</v>
+        <v>2.1523</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>5000</v>
+        <v>5230</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5k</t>
+          <t>5.23k</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>25</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>75</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>3</v>
@@ -984,10 +992,10 @@
         <v>9</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
@@ -995,24 +1003,24 @@
         <v>6</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>2</v>
+        <v>1.6673</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>10000</v>
+        <v>8720</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>8.72k</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="H7" s="5" t="n">
         <v>3</v>
@@ -1021,10 +1029,10 @@
         <v>12</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>180</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1032,24 +1040,24 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>2</v>
+        <v>1.3761</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>20k</t>
+          <t>12k</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="H8" s="5" t="n">
         <v>2</v>
@@ -1058,10 +1066,10 @@
         <v>14</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>210</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1069,24 +1077,24 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1.18</v>
+        <v>1.325</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>23600</v>
+        <v>15900</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>23.6k</t>
+          <t>15.9k</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>2</v>
@@ -1095,10 +1103,10 @@
         <v>16</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>240</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1106,24 +1114,24 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1.18</v>
+        <v>1.1635</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>27848</v>
+        <v>18500</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>27.8k</t>
+          <t>18.5k</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>115</v>
+        <v>45</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>2</v>
@@ -1132,10 +1140,10 @@
         <v>18</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>270</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
@@ -1143,24 +1151,24 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1.18</v>
+        <v>1.173</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>32861</v>
+        <v>21700</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>32.8k</t>
+          <t>21.7k</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>2</v>
@@ -1169,10 +1177,10 @@
         <v>20</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>300</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
@@ -1180,24 +1188,24 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1.18</v>
+        <v>1.129</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>38776</v>
+        <v>24500</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>38.7k</t>
+          <t>24.5k</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>125</v>
+        <v>55</v>
       </c>
       <c r="H12" s="5" t="n">
         <v>2</v>
@@ -1206,10 +1214,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>335</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
@@ -1217,24 +1225,24 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>1.18</v>
+        <v>1.1388</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>45756</v>
+        <v>27900</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>45.7k</t>
+          <t>27.9k</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="H13" s="5" t="n">
         <v>2</v>
@@ -1243,10 +1251,10 @@
         <v>24</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>370</v>
+        <v>210</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1254,24 +1262,24 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0753</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>53992</v>
+        <v>30000</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>53.9k</t>
+          <t>30k</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="H14" s="5" t="n">
         <v>2</v>
@@ -1280,10 +1288,10 @@
         <v>26</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>405</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1291,24 +1299,24 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0533</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>63711</v>
+        <v>31600</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>63.7k</t>
+          <t>31.6k</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="H15" s="5" t="n">
         <v>2</v>
@@ -1317,10 +1325,10 @@
         <v>28</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>440</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -1328,24 +1336,24 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="n">
-        <v>15</v>
+        <v>22.5</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1.18</v>
+        <v>1.1203</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>75179</v>
+        <v>35400</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>75.1k</t>
+          <t>35.4k</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>2</v>
@@ -1354,10 +1362,10 @@
         <v>30</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>475</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -1365,24 +1373,24 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0621</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>88711</v>
+        <v>37600</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>88.7k</t>
+          <t>37.6k</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="H17" s="5" t="n">
         <v>2</v>
@@ -1391,10 +1399,10 @@
         <v>32</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>510</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -1402,24 +1410,24 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>17</v>
+        <v>25.5</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0638</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>104679</v>
+        <v>40000</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>104k</t>
+          <t>40k</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="H18" s="5" t="n">
         <v>2</v>
@@ -1428,10 +1436,10 @@
         <v>34</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>545</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -1439,24 +1447,24 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>123521</v>
+        <v>42000</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>123k</t>
+          <t>42k</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>160</v>
+        <v>90</v>
       </c>
       <c r="H19" s="5" t="n">
         <v>2</v>
@@ -1465,10 +1473,10 @@
         <v>36</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>580</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
@@ -1476,24 +1484,24 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>19</v>
+        <v>28.5</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0571</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>145755</v>
+        <v>44400</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>145k</t>
+          <t>44.4k</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>165</v>
+        <v>95</v>
       </c>
       <c r="H20" s="5" t="n">
         <v>2</v>
@@ -1502,10 +1510,10 @@
         <v>38</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>615</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1513,24 +1521,24 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0315</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>171991</v>
+        <v>45800</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>171k</t>
+          <t>45.8k</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="H21" s="5" t="n">
         <v>2</v>
@@ -1539,10 +1547,10 @@
         <v>40</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>650</v>
+        <v>370</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1550,24 +1558,24 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>21</v>
+        <v>31.5</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0371</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>202949</v>
+        <v>47500</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>202k</t>
+          <t>47.5k</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="H22" s="5" t="n">
         <v>2</v>
@@ -1576,10 +1584,10 @@
         <v>42</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>690</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -1587,24 +1595,24 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0505</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>239480</v>
+        <v>49900</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>239k</t>
+          <t>49.9k</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>2</v>
@@ -1613,10 +1621,10 @@
         <v>44</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>730</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -1624,24 +1632,24 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>23</v>
+        <v>34.5</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0301</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>282586</v>
+        <v>51400</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>282k</t>
+          <t>51.4k</t>
         </is>
       </c>
       <c r="F24" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>185</v>
+        <v>115</v>
       </c>
       <c r="H24" s="5" t="n">
         <v>2</v>
@@ -1650,10 +1658,10 @@
         <v>46</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>770</v>
+        <v>439</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -1661,24 +1669,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0272</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>333451</v>
+        <v>52800</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>333k</t>
+          <t>52.8k</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="H25" s="5" t="n">
         <v>2</v>
@@ -1687,10 +1695,10 @@
         <v>48</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>810</v>
+        <v>462</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -1698,24 +1706,24 @@
         <v>25</v>
       </c>
       <c r="B26" s="7" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>1.18</v>
+        <v>1.036</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>393472</v>
+        <v>54700</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>393k</t>
+          <t>54.7k</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>2</v>
@@ -1724,10 +1732,10 @@
         <v>50</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>850</v>
+        <v>485</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -1735,24 +1743,24 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0146</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>464297</v>
+        <v>55500</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>464k</t>
+          <t>55.5k</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>2</v>
@@ -1761,10 +1769,10 @@
         <v>52</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>890</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -1772,24 +1780,24 @@
         <v>27</v>
       </c>
       <c r="B28" s="7" t="n">
-        <v>27</v>
+        <v>40.5</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>1.18</v>
+        <v>1.036</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>547870</v>
+        <v>57500</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>547k</t>
+          <t>57.5k</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>205</v>
+        <v>135</v>
       </c>
       <c r="H28" s="5" t="n">
         <v>2</v>
@@ -1798,10 +1806,10 @@
         <v>54</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>930</v>
+        <v>531</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -1809,24 +1817,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="7" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0174</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>646487</v>
+        <v>58500</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>646k</t>
+          <t>58.5k</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="H29" s="5" t="n">
         <v>2</v>
@@ -1835,10 +1843,10 @@
         <v>56</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>970</v>
+        <v>554</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -1846,24 +1854,24 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>29</v>
+        <v>43.5</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0376</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>762855</v>
+        <v>60700</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>762k</t>
+          <t>60.7k</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="H30" s="5" t="n">
         <v>2</v>
@@ -1872,10 +1880,10 @@
         <v>58</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>1010</v>
+        <v>577</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
@@ -1883,24 +1891,24 @@
         <v>30</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1.18</v>
+        <v>1.0132</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>900169</v>
+        <v>61500</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>900k</t>
+          <t>61.5k</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="H31" s="5" t="n">
         <v>2</v>
@@ -1909,10 +1917,10 @@
         <v>60</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>1050</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
@@ -1920,24 +1928,24 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>31</v>
+        <v>46.5</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1.1</v>
+        <v>1.039</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>990186</v>
+        <v>63900</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>990k</t>
+          <t>63.9k</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>225</v>
+        <v>155</v>
       </c>
       <c r="H32" s="5" t="n">
         <v>2</v>
@@ -1946,10 +1954,10 @@
         <v>62</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>1095</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -1957,24 +1965,24 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0188</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>1089205</v>
+        <v>65100</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>1.08m</t>
+          <t>65.1k</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>230</v>
+        <v>160</v>
       </c>
       <c r="H33" s="5" t="n">
         <v>2</v>
@@ -1983,10 +1991,10 @@
         <v>64</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>1140</v>
+        <v>652</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
@@ -1994,24 +2002,24 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>33</v>
+        <v>49.5</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0108</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>1198126</v>
+        <v>65800</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>1.19m</t>
+          <t>65.8k</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>235</v>
+        <v>165</v>
       </c>
       <c r="H34" s="5" t="n">
         <v>2</v>
@@ -2020,10 +2028,10 @@
         <v>66</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>1185</v>
+        <v>678</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
@@ -2031,24 +2039,24 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0304</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>1317939</v>
+        <v>67800</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>1.31m</t>
+          <t>67.8k</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="H35" s="5" t="n">
         <v>2</v>
@@ -2057,10 +2065,10 @@
         <v>68</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>1230</v>
+        <v>704</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
@@ -2068,24 +2076,24 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>35</v>
+        <v>52.5</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>1449733</v>
+        <v>68200</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>1.44m</t>
+          <t>68.2k</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>245</v>
+        <v>175</v>
       </c>
       <c r="H36" s="5" t="n">
         <v>2</v>
@@ -2094,10 +2102,10 @@
         <v>70</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>1275</v>
+        <v>730</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
@@ -2105,24 +2113,24 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0279</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>1594706</v>
+        <v>70100</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>1.59m</t>
+          <t>70.1k</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="H37" s="5" t="n">
         <v>2</v>
@@ -2131,10 +2139,10 @@
         <v>72</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>1320</v>
+        <v>756</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
@@ -2142,24 +2150,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>37</v>
+        <v>55.5</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0214</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>1754177</v>
+        <v>71600</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>1.75m</t>
+          <t>71.6k</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="H38" s="5" t="n">
         <v>2</v>
@@ -2168,10 +2176,10 @@
         <v>74</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>1365</v>
+        <v>782</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -2179,24 +2187,24 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0363</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>1929595</v>
+        <v>74200</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>1.92m</t>
+          <t>74.2k</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>260</v>
+        <v>190</v>
       </c>
       <c r="H39" s="5" t="n">
         <v>2</v>
@@ -2205,10 +2213,10 @@
         <v>76</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>1410</v>
+        <v>808</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
@@ -2216,24 +2224,24 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>39</v>
+        <v>58.5</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>2122554</v>
+        <v>74300</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>2.12m</t>
+          <t>74.3k</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>265</v>
+        <v>195</v>
       </c>
       <c r="H40" s="5" t="n">
         <v>2</v>
@@ -2242,10 +2250,10 @@
         <v>78</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>1455</v>
+        <v>834</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
@@ -2253,24 +2261,24 @@
         <v>40</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>2334809</v>
+        <v>74500</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>2.33m</t>
+          <t>74.5k</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>270</v>
+        <v>200</v>
       </c>
       <c r="H41" s="5" t="n">
         <v>2</v>
@@ -2279,10 +2287,10 @@
         <v>80</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>1500</v>
+        <v>860</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
@@ -2290,24 +2298,24 @@
         <v>41</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>41</v>
+        <v>61.5</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0134</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>2568290</v>
+        <v>75500</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>2.56m</t>
+          <t>75.5k</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>275</v>
+        <v>205</v>
       </c>
       <c r="H42" s="5" t="n">
         <v>2</v>
@@ -2316,10 +2324,10 @@
         <v>82</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>1550</v>
+        <v>889</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
@@ -2327,24 +2335,24 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0106</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>2825119</v>
+        <v>76300</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>2.82m</t>
+          <t>76.3k</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>280</v>
+        <v>210</v>
       </c>
       <c r="H43" s="5" t="n">
         <v>2</v>
@@ -2353,10 +2361,10 @@
         <v>84</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>1600</v>
+        <v>918</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
@@ -2364,24 +2372,24 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>43</v>
+        <v>64.5</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0157</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>3107631</v>
+        <v>77500</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>3.1m</t>
+          <t>77.5k</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>285</v>
+        <v>215</v>
       </c>
       <c r="H44" s="5" t="n">
         <v>2</v>
@@ -2390,10 +2398,10 @@
         <v>86</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>1650</v>
+        <v>947</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -2401,24 +2409,24 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0116</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>3418394</v>
+        <v>78400</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>3.41m</t>
+          <t>78.4k</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="H45" s="5" t="n">
         <v>2</v>
@@ -2427,10 +2435,10 @@
         <v>88</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>1700</v>
+        <v>976</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -2438,24 +2446,24 @@
         <v>45</v>
       </c>
       <c r="B46" s="7" t="n">
-        <v>45</v>
+        <v>67.5</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0217</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>3760233</v>
+        <v>80100</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>3.76m</t>
+          <t>80.1k</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>295</v>
+        <v>225</v>
       </c>
       <c r="H46" s="5" t="n">
         <v>2</v>
@@ -2464,10 +2472,10 @@
         <v>90</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>1750</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
@@ -2475,24 +2483,24 @@
         <v>46</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0175</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>4136256</v>
+        <v>81500</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>4.13m</t>
+          <t>81.5k</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
       <c r="H47" s="5" t="n">
         <v>2</v>
@@ -2501,10 +2509,10 @@
         <v>92</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>1800</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
@@ -2512,24 +2520,24 @@
         <v>47</v>
       </c>
       <c r="B48" s="7" t="n">
-        <v>47</v>
+        <v>70.5</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>4549882</v>
+        <v>81600</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>4.54m</t>
+          <t>81.6k</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>305</v>
+        <v>235</v>
       </c>
       <c r="H48" s="5" t="n">
         <v>2</v>
@@ -2538,10 +2546,10 @@
         <v>94</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>1850</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
@@ -2549,24 +2557,24 @@
         <v>48</v>
       </c>
       <c r="B49" s="7" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>5004870</v>
+        <v>81800</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>81.8k</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="H49" s="5" t="n">
         <v>2</v>
@@ -2575,10 +2583,10 @@
         <v>96</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>1900</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
@@ -2586,24 +2594,24 @@
         <v>49</v>
       </c>
       <c r="B50" s="7" t="n">
-        <v>49</v>
+        <v>73.5</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0147</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>5505357</v>
+        <v>83000</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>5.5m</t>
+          <t>83k</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>315</v>
+        <v>245</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>2</v>
@@ -2612,10 +2620,10 @@
         <v>98</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>1950</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
@@ -2623,24 +2631,24 @@
         <v>50</v>
       </c>
       <c r="B51" s="7" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>6055893</v>
+        <v>83200</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>6.05m</t>
+          <t>83.2k</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="H51" s="5" t="n">
         <v>2</v>
@@ -2649,10 +2657,10 @@
         <v>100</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>2000</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
@@ -2660,24 +2668,24 @@
         <v>51</v>
       </c>
       <c r="B52" s="7" t="n">
-        <v>51</v>
+        <v>76.5</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>1.1</v>
+        <v>1.024</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>6661482</v>
+        <v>85200</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>6.66m</t>
+          <t>85.2k</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>325</v>
+        <v>255</v>
       </c>
       <c r="H52" s="5" t="n">
         <v>3</v>
@@ -2686,10 +2694,10 @@
         <v>103</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>2055</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
@@ -2697,24 +2705,24 @@
         <v>52</v>
       </c>
       <c r="B53" s="7" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>7327630</v>
+        <v>86000</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>7.32m</t>
+          <t>86k</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G53" s="7" t="n">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="H53" s="5" t="n">
         <v>3</v>
@@ -2723,10 +2731,10 @@
         <v>106</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>2110</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
@@ -2734,24 +2742,24 @@
         <v>53</v>
       </c>
       <c r="B54" s="7" t="n">
-        <v>53</v>
+        <v>79.5</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0233</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>8060393</v>
+        <v>88000</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>8.06m</t>
+          <t>88k</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>335</v>
+        <v>265</v>
       </c>
       <c r="H54" s="5" t="n">
         <v>3</v>
@@ -2760,10 +2768,10 @@
         <v>109</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>2165</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
@@ -2771,24 +2779,24 @@
         <v>54</v>
       </c>
       <c r="B55" s="7" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0432</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>8866432</v>
+        <v>91800</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>8.86m</t>
+          <t>91.8k</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G55" s="7" t="n">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="H55" s="5" t="n">
         <v>3</v>
@@ -2797,10 +2805,10 @@
         <v>112</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>2220</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
@@ -2808,24 +2816,24 @@
         <v>55</v>
       </c>
       <c r="B56" s="7" t="n">
-        <v>55</v>
+        <v>82.5</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0109</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>9753075</v>
+        <v>92800</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>9.75m</t>
+          <t>92.8k</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>345</v>
+        <v>275</v>
       </c>
       <c r="H56" s="5" t="n">
         <v>3</v>
@@ -2834,10 +2842,10 @@
         <v>115</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>2275</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -2845,24 +2853,24 @@
         <v>56</v>
       </c>
       <c r="B57" s="7" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0129</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>10728382</v>
+        <v>94000</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>10.7m</t>
+          <t>94k</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>350</v>
+        <v>280</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>3</v>
@@ -2871,10 +2879,10 @@
         <v>118</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>2330</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
@@ -2882,24 +2890,24 @@
         <v>57</v>
       </c>
       <c r="B58" s="7" t="n">
-        <v>57</v>
+        <v>85.5</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0149</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>11801220</v>
+        <v>95400</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>11.8m</t>
+          <t>95.4k</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>355</v>
+        <v>285</v>
       </c>
       <c r="H58" s="5" t="n">
         <v>3</v>
@@ -2908,10 +2916,10 @@
         <v>121</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>2385</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
@@ -2919,24 +2927,24 @@
         <v>58</v>
       </c>
       <c r="B59" s="7" t="n">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0136</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>12981342</v>
+        <v>96700</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>12.9m</t>
+          <t>96.7k</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G59" s="7" t="n">
-        <v>360</v>
+        <v>290</v>
       </c>
       <c r="H59" s="5" t="n">
         <v>3</v>
@@ -2945,10 +2953,10 @@
         <v>124</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>2440</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
@@ -2956,24 +2964,24 @@
         <v>59</v>
       </c>
       <c r="B60" s="7" t="n">
-        <v>59</v>
+        <v>88.5</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0259</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>14279476</v>
+        <v>99200</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>14.2m</t>
+          <t>99.2k</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G60" s="7" t="n">
-        <v>365</v>
+        <v>295</v>
       </c>
       <c r="H60" s="5" t="n">
         <v>3</v>
@@ -2982,10 +2990,10 @@
         <v>127</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>2495</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -2993,24 +3001,24 @@
         <v>60</v>
       </c>
       <c r="B61" s="7" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0181</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>15707424</v>
+        <v>101000</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>15.7m</t>
+          <t>101k</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G61" s="7" t="n">
-        <v>370</v>
+        <v>300</v>
       </c>
       <c r="H61" s="5" t="n">
         <v>3</v>
@@ -3019,10 +3027,10 @@
         <v>130</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>2550</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
@@ -3030,24 +3038,24 @@
         <v>61</v>
       </c>
       <c r="B62" s="7" t="n">
-        <v>61</v>
+        <v>91.5</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0495</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>17278166</v>
+        <v>106000</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>17.2m</t>
+          <t>106k</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>375</v>
+        <v>305</v>
       </c>
       <c r="H62" s="5" t="n">
         <v>3</v>
@@ -3056,10 +3064,10 @@
         <v>133</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>2610</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
@@ -3067,24 +3075,24 @@
         <v>62</v>
       </c>
       <c r="B63" s="7" t="n">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0472</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>19005983</v>
+        <v>111000</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>19m</t>
+          <t>111k</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>380</v>
+        <v>310</v>
       </c>
       <c r="H63" s="5" t="n">
         <v>3</v>
@@ -3093,10 +3101,10 @@
         <v>136</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>2670</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -3104,24 +3112,24 @@
         <v>63</v>
       </c>
       <c r="B64" s="7" t="n">
-        <v>63</v>
+        <v>94.5</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>1.1</v>
+        <v>1.018</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>20906581</v>
+        <v>113000</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>20.9m</t>
+          <t>113k</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>385</v>
+        <v>315</v>
       </c>
       <c r="H64" s="5" t="n">
         <v>3</v>
@@ -3130,10 +3138,10 @@
         <v>139</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>2730</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
@@ -3141,24 +3149,24 @@
         <v>64</v>
       </c>
       <c r="B65" s="7" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>22997239</v>
+        <v>114000</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>22.9m</t>
+          <t>114k</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G65" s="7" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="H65" s="5" t="n">
         <v>3</v>
@@ -3167,10 +3175,10 @@
         <v>142</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>2790</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
@@ -3178,24 +3186,24 @@
         <v>65</v>
       </c>
       <c r="B66" s="7" t="n">
-        <v>65</v>
+        <v>97.5</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0175</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>25296963</v>
+        <v>116000</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>25.2m</t>
+          <t>116k</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G66" s="7" t="n">
-        <v>395</v>
+        <v>325</v>
       </c>
       <c r="H66" s="5" t="n">
         <v>3</v>
@@ -3204,10 +3212,10 @@
         <v>145</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>2850</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
@@ -3215,24 +3223,24 @@
         <v>66</v>
       </c>
       <c r="B67" s="7" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0259</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>27826659</v>
+        <v>119000</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>27.8m</t>
+          <t>119k</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>3</v>
@@ -3241,10 +3249,10 @@
         <v>148</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K67" s="8" t="n">
-        <v>2910</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
@@ -3252,24 +3260,24 @@
         <v>67</v>
       </c>
       <c r="B68" s="7" t="n">
-        <v>67</v>
+        <v>100.5</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0504</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>30609325</v>
+        <v>125000</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>30.6m</t>
+          <t>125k</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="H68" s="5" t="n">
         <v>3</v>
@@ -3278,10 +3286,10 @@
         <v>151</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>2970</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
@@ -3289,24 +3297,24 @@
         <v>68</v>
       </c>
       <c r="B69" s="7" t="n">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>1.1</v>
+        <v>1.024</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>33670258</v>
+        <v>128000</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>33.6m</t>
+          <t>128k</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>3</v>
@@ -3315,10 +3323,10 @@
         <v>154</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>3030</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
@@ -3326,24 +3334,24 @@
         <v>69</v>
       </c>
       <c r="B70" s="7" t="n">
-        <v>69</v>
+        <v>103.5</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0391</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>37037284</v>
+        <v>133000</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>37m</t>
+          <t>133k</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>415</v>
+        <v>345</v>
       </c>
       <c r="H70" s="5" t="n">
         <v>3</v>
@@ -3352,10 +3360,10 @@
         <v>157</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>3090</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
@@ -3363,24 +3371,24 @@
         <v>70</v>
       </c>
       <c r="B71" s="7" t="n">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0451</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>40741012</v>
+        <v>139000</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>40.7m</t>
+          <t>139k</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>3</v>
@@ -3389,10 +3397,10 @@
         <v>160</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>3150</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
@@ -3400,24 +3408,24 @@
         <v>71</v>
       </c>
       <c r="B72" s="7" t="n">
-        <v>71</v>
+        <v>106.5</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>44815113</v>
+        <v>139001</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>44.8m</t>
+          <t>139k</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G72" s="7" t="n">
-        <v>425</v>
+        <v>355</v>
       </c>
       <c r="H72" s="5" t="n">
         <v>3</v>
@@ -3426,10 +3434,10 @@
         <v>163</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>3215</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
@@ -3437,24 +3445,24 @@
         <v>72</v>
       </c>
       <c r="B73" s="7" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="C73" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>49296624</v>
+        <v>139002</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>49.2m</t>
+          <t>139k</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>430</v>
+        <v>360</v>
       </c>
       <c r="H73" s="5" t="n">
         <v>3</v>
@@ -3463,10 +3471,10 @@
         <v>166</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>3280</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
@@ -3474,24 +3482,24 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>73</v>
+        <v>109.5</v>
       </c>
       <c r="C74" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>54226286</v>
+        <v>140000</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>54.2m</t>
+          <t>140k</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>435</v>
+        <v>365</v>
       </c>
       <c r="H74" s="5" t="n">
         <v>3</v>
@@ -3500,10 +3508,10 @@
         <v>169</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>3345</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
@@ -3511,24 +3519,24 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="n">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0143</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>59648915</v>
+        <v>142000</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>59.6m</t>
+          <t>142k</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>440</v>
+        <v>370</v>
       </c>
       <c r="H75" s="5" t="n">
         <v>3</v>
@@ -3537,10 +3545,10 @@
         <v>172</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>3410</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
@@ -3548,24 +3556,24 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>75</v>
+        <v>112.5</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>65613807</v>
+        <v>143000</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>65.6m</t>
+          <t>143k</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G76" s="7" t="n">
-        <v>445</v>
+        <v>375</v>
       </c>
       <c r="H76" s="5" t="n">
         <v>3</v>
@@ -3574,10 +3582,10 @@
         <v>175</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>3475</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
@@ -3585,24 +3593,24 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>72175188</v>
+        <v>143001</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>72.1m</t>
+          <t>143k</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="H77" s="5" t="n">
         <v>3</v>
@@ -3611,10 +3619,10 @@
         <v>178</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K77" s="8" t="n">
-        <v>3540</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
@@ -3622,24 +3630,24 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>77</v>
+        <v>115.5</v>
       </c>
       <c r="C78" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>79392707</v>
+        <v>144000</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>79.3m</t>
+          <t>144k</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>455</v>
+        <v>385</v>
       </c>
       <c r="H78" s="5" t="n">
         <v>3</v>
@@ -3648,10 +3656,10 @@
         <v>181</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K78" s="8" t="n">
-        <v>3605</v>
+        <v>2086</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1">
@@ -3659,24 +3667,24 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="n">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0139</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>87331978</v>
+        <v>146000</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>87.3m</t>
+          <t>146k</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>460</v>
+        <v>390</v>
       </c>
       <c r="H79" s="5" t="n">
         <v>3</v>
@@ -3685,10 +3693,10 @@
         <v>184</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K79" s="8" t="n">
-        <v>3670</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
@@ -3696,24 +3704,24 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>79</v>
+        <v>118.5</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>1.1</v>
+        <v>1.0137</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>96065176</v>
+        <v>148000</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>96m</t>
+          <t>148k</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>465</v>
+        <v>395</v>
       </c>
       <c r="H80" s="5" t="n">
         <v>3</v>
@@ -3722,10 +3730,10 @@
         <v>187</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K80" s="8" t="n">
-        <v>3735</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
@@ -3733,24 +3741,24 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C81" s="6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>105671694</v>
+        <v>149000</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>105m</t>
+          <t>149k</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>470</v>
+        <v>400</v>
       </c>
       <c r="H81" s="5" t="n">
         <v>3</v>
@@ -3759,10 +3767,10 @@
         <v>190</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K81" s="8" t="n">
-        <v>3800</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -3770,24 +3778,24 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="n">
-        <v>81</v>
+        <v>121.5</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0134</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>112011996</v>
+        <v>151000</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>112m</t>
+          <t>151k</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G82" s="7" t="n">
-        <v>475</v>
+        <v>405</v>
       </c>
       <c r="H82" s="5" t="n">
         <v>3</v>
@@ -3796,10 +3804,10 @@
         <v>193</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K82" s="8" t="n">
-        <v>3870</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
@@ -3807,24 +3815,24 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="n">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0199</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>118732716</v>
+        <v>154000</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>118m</t>
+          <t>154k</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>480</v>
+        <v>410</v>
       </c>
       <c r="H83" s="5" t="n">
         <v>3</v>
@@ -3833,10 +3841,10 @@
         <v>196</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K83" s="8" t="n">
-        <v>3940</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="84" ht="19" customHeight="1">
@@ -3844,24 +3852,24 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="n">
-        <v>83</v>
+        <v>124.5</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>1.06</v>
+        <v>1.026</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>125856679</v>
+        <v>158000</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>125m</t>
+          <t>158k</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>485</v>
+        <v>415</v>
       </c>
       <c r="H84" s="5" t="n">
         <v>3</v>
@@ -3870,10 +3878,10 @@
         <v>199</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K84" s="8" t="n">
-        <v>4010</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="85" ht="19" customHeight="1">
@@ -3881,24 +3889,24 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="n">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0127</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>133408080</v>
+        <v>160000</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>133m</t>
+          <t>160k</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>490</v>
+        <v>420</v>
       </c>
       <c r="H85" s="5" t="n">
         <v>3</v>
@@ -3907,10 +3915,10 @@
         <v>202</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K85" s="8" t="n">
-        <v>4080</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="86" ht="19" customHeight="1">
@@ -3918,24 +3926,24 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="n">
-        <v>85</v>
+        <v>127.5</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>1.06</v>
+        <v>1.025</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>141412565</v>
+        <v>164000</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>141m</t>
+          <t>164k</t>
         </is>
       </c>
       <c r="F86" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>495</v>
+        <v>425</v>
       </c>
       <c r="H86" s="5" t="n">
         <v>3</v>
@@ -3944,10 +3952,10 @@
         <v>205</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K86" s="8" t="n">
-        <v>4150</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
@@ -3955,24 +3963,24 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="n">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="C87" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>149897319</v>
+        <v>165000</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>149m</t>
+          <t>165k</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G87" s="7" t="n">
-        <v>500</v>
+        <v>430</v>
       </c>
       <c r="H87" s="5" t="n">
         <v>3</v>
@@ -3981,10 +3989,10 @@
         <v>208</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K87" s="8" t="n">
-        <v>4220</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -3992,24 +4000,24 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="n">
-        <v>87</v>
+        <v>130.5</v>
       </c>
       <c r="C88" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>158891158</v>
+        <v>165001</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>158m</t>
+          <t>165k</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>505</v>
+        <v>435</v>
       </c>
       <c r="H88" s="5" t="n">
         <v>3</v>
@@ -4018,10 +4026,10 @@
         <v>211</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K88" s="8" t="n">
-        <v>4290</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -4029,24 +4037,24 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="C89" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>168424627</v>
+        <v>166000</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>168m</t>
+          <t>166k</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>510</v>
+        <v>440</v>
       </c>
       <c r="H89" s="5" t="n">
         <v>3</v>
@@ -4055,10 +4063,10 @@
         <v>214</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K89" s="8" t="n">
-        <v>4360</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
@@ -4066,24 +4074,24 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="n">
-        <v>89</v>
+        <v>133.5</v>
       </c>
       <c r="C90" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>178530105</v>
+        <v>167000</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>178m</t>
+          <t>167k</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G90" s="7" t="n">
-        <v>515</v>
+        <v>445</v>
       </c>
       <c r="H90" s="5" t="n">
         <v>3</v>
@@ -4092,10 +4100,10 @@
         <v>217</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K90" s="8" t="n">
-        <v>4430</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="91" ht="19" customHeight="1">
@@ -4103,24 +4111,24 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>189241911</v>
+        <v>168000</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>189m</t>
+          <t>168k</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G91" s="7" t="n">
-        <v>520</v>
+        <v>450</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>3</v>
@@ -4129,10 +4137,10 @@
         <v>220</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="K91" s="8" t="n">
-        <v>4500</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
@@ -4140,24 +4148,24 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="n">
-        <v>91</v>
+        <v>136.5</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0179</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>200596426</v>
+        <v>171000</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>200m</t>
+          <t>171k</t>
         </is>
       </c>
       <c r="F92" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>525</v>
+        <v>455</v>
       </c>
       <c r="H92" s="5" t="n">
         <v>3</v>
@@ -4166,10 +4174,10 @@
         <v>223</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K92" s="8" t="n">
-        <v>4575</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
@@ -4177,24 +4185,24 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="n">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="C93" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>212632212</v>
+        <v>172000</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>212m</t>
+          <t>172k</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>530</v>
+        <v>460</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>3</v>
@@ -4203,10 +4211,10 @@
         <v>226</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K93" s="8" t="n">
-        <v>4650</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
@@ -4214,24 +4222,24 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="n">
-        <v>93</v>
+        <v>139.5</v>
       </c>
       <c r="C94" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0174</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>225390145</v>
+        <v>175000</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>225m</t>
+          <t>175k</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>535</v>
+        <v>465</v>
       </c>
       <c r="H94" s="5" t="n">
         <v>3</v>
@@ -4240,10 +4248,10 @@
         <v>229</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K94" s="8" t="n">
-        <v>4725</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
@@ -4251,24 +4259,24 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="n">
-        <v>94</v>
+        <v>141</v>
       </c>
       <c r="C95" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0114</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>238913554</v>
+        <v>177000</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>238m</t>
+          <t>177k</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G95" s="7" t="n">
-        <v>540</v>
+        <v>470</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>3</v>
@@ -4277,10 +4285,10 @@
         <v>232</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K95" s="8" t="n">
-        <v>4800</v>
+        <v>2786</v>
       </c>
     </row>
     <row r="96" ht="19" customHeight="1">
@@ -4288,24 +4296,24 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="n">
-        <v>95</v>
+        <v>142.5</v>
       </c>
       <c r="C96" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>253248367</v>
+        <v>178000</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>253m</t>
+          <t>178k</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G96" s="7" t="n">
-        <v>545</v>
+        <v>475</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>3</v>
@@ -4314,10 +4322,10 @@
         <v>235</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K96" s="8" t="n">
-        <v>4875</v>
+        <v>2830</v>
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
@@ -4325,24 +4333,24 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="n">
-        <v>96</v>
+        <v>144</v>
       </c>
       <c r="C97" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>268443269</v>
+        <v>179000</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>268m</t>
+          <t>179k</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>550</v>
+        <v>480</v>
       </c>
       <c r="H97" s="5" t="n">
         <v>3</v>
@@ -4351,10 +4359,10 @@
         <v>238</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K97" s="8" t="n">
-        <v>4950</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="98" ht="19" customHeight="1">
@@ -4362,24 +4370,24 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="n">
-        <v>97</v>
+        <v>145.5</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0112</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>284549865</v>
+        <v>181000</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>284m</t>
+          <t>181k</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>555</v>
+        <v>485</v>
       </c>
       <c r="H98" s="5" t="n">
         <v>3</v>
@@ -4388,10 +4396,10 @@
         <v>241</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K98" s="8" t="n">
-        <v>5025</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
@@ -4399,24 +4407,24 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="n">
-        <v>98</v>
+        <v>147</v>
       </c>
       <c r="C99" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0221</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>301622857</v>
+        <v>185000</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>301m</t>
+          <t>185k</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G99" s="7" t="n">
-        <v>560</v>
+        <v>490</v>
       </c>
       <c r="H99" s="5" t="n">
         <v>3</v>
@@ -4425,10 +4433,10 @@
         <v>244</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K99" s="8" t="n">
-        <v>5100</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
@@ -4436,24 +4444,24 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="n">
-        <v>99</v>
+        <v>148.5</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>1.06</v>
+        <v>1.027</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>319720228</v>
+        <v>190000</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>319m</t>
+          <t>190k</t>
         </is>
       </c>
       <c r="F100" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G100" s="7" t="n">
-        <v>565</v>
+        <v>495</v>
       </c>
       <c r="H100" s="5" t="n">
         <v>3</v>
@@ -4462,10 +4470,10 @@
         <v>247</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K100" s="8" t="n">
-        <v>5175</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="101" ht="19" customHeight="1">
@@ -4473,24 +4481,24 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C101" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0105</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>338903442</v>
+        <v>192000</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>338m</t>
+          <t>192k</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>570</v>
+        <v>500</v>
       </c>
       <c r="H101" s="5" t="n">
         <v>3</v>
@@ -4499,10 +4507,10 @@
         <v>250</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="K101" s="8" t="n">
-        <v>5250</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
@@ -4510,24 +4518,24 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="n">
-        <v>101</v>
+        <v>151.5</v>
       </c>
       <c r="C102" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0104</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>359237649</v>
+        <v>194000</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>359m</t>
+          <t>194k</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G102" s="7" t="n">
-        <v>575</v>
+        <v>505</v>
       </c>
       <c r="H102" s="5" t="n">
         <v>3</v>
@@ -4536,10 +4544,10 @@
         <v>253</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K102" s="8" t="n">
-        <v>5330</v>
+        <v>3097</v>
       </c>
     </row>
     <row r="103" ht="19" customHeight="1">
@@ -4547,24 +4555,24 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="C103" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0103</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>380791908</v>
+        <v>196000</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>380m</t>
+          <t>196k</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="H103" s="5" t="n">
         <v>3</v>
@@ -4573,10 +4581,10 @@
         <v>256</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K103" s="8" t="n">
-        <v>5410</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="104" ht="19" customHeight="1">
@@ -4584,24 +4592,24 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="n">
-        <v>103</v>
+        <v>154.5</v>
       </c>
       <c r="C104" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0102</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>403639422</v>
+        <v>198000</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>403m</t>
+          <t>198k</t>
         </is>
       </c>
       <c r="F104" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>585</v>
+        <v>515</v>
       </c>
       <c r="H104" s="5" t="n">
         <v>3</v>
@@ -4610,10 +4618,10 @@
         <v>259</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K104" s="8" t="n">
-        <v>5490</v>
+        <v>3191</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -4621,24 +4629,24 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="n">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="C105" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0101</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>427857787</v>
+        <v>200000</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>427m</t>
+          <t>200k</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>590</v>
+        <v>520</v>
       </c>
       <c r="H105" s="5" t="n">
         <v>3</v>
@@ -4647,10 +4655,10 @@
         <v>262</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K105" s="8" t="n">
-        <v>5570</v>
+        <v>3238</v>
       </c>
     </row>
     <row r="106" ht="19" customHeight="1">
@@ -4658,24 +4666,24 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="n">
-        <v>105</v>
+        <v>157.5</v>
       </c>
       <c r="C106" s="6" t="n">
-        <v>1.06</v>
+        <v>1.015</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>453529254</v>
+        <v>203000</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>453m</t>
+          <t>203k</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>595</v>
+        <v>525</v>
       </c>
       <c r="H106" s="5" t="n">
         <v>3</v>
@@ -4684,10 +4692,10 @@
         <v>265</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K106" s="8" t="n">
-        <v>5650</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="107" ht="19" customHeight="1">
@@ -4695,24 +4703,24 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="n">
-        <v>106</v>
+        <v>159</v>
       </c>
       <c r="C107" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>480741009</v>
+        <v>205000</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>480m</t>
+          <t>205k</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>600</v>
+        <v>530</v>
       </c>
       <c r="H107" s="5" t="n">
         <v>3</v>
@@ -4721,10 +4729,10 @@
         <v>268</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K107" s="8" t="n">
-        <v>5730</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="108" ht="19" customHeight="1">
@@ -4732,24 +4740,24 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="n">
-        <v>107</v>
+        <v>160.5</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>509585470</v>
+        <v>207000</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>509m</t>
+          <t>207k</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>605</v>
+        <v>535</v>
       </c>
       <c r="H108" s="5" t="n">
         <v>3</v>
@@ -4758,10 +4766,10 @@
         <v>271</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K108" s="8" t="n">
-        <v>5810</v>
+        <v>3379</v>
       </c>
     </row>
     <row r="109" ht="19" customHeight="1">
@@ -4769,24 +4777,24 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="n">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="C109" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>540160598</v>
+        <v>209000</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>540m</t>
+          <t>209k</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G109" s="7" t="n">
-        <v>610</v>
+        <v>540</v>
       </c>
       <c r="H109" s="5" t="n">
         <v>3</v>
@@ -4795,10 +4803,10 @@
         <v>274</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K109" s="8" t="n">
-        <v>5890</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
@@ -4806,24 +4814,24 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="n">
-        <v>109</v>
+        <v>163.5</v>
       </c>
       <c r="C110" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>572570234</v>
+        <v>211000</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>572m</t>
+          <t>211k</t>
         </is>
       </c>
       <c r="F110" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G110" s="7" t="n">
-        <v>615</v>
+        <v>545</v>
       </c>
       <c r="H110" s="5" t="n">
         <v>3</v>
@@ -4832,10 +4840,10 @@
         <v>277</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K110" s="8" t="n">
-        <v>5970</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="111" ht="19" customHeight="1">
@@ -4843,24 +4851,24 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="n">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="C111" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>606924448</v>
+        <v>213000</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>606m</t>
+          <t>213k</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>620</v>
+        <v>550</v>
       </c>
       <c r="H111" s="5" t="n">
         <v>3</v>
@@ -4869,10 +4877,10 @@
         <v>280</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="K111" s="8" t="n">
-        <v>6050</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="112" ht="19" customHeight="1">
@@ -4880,24 +4888,24 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="n">
-        <v>111</v>
+        <v>166.5</v>
       </c>
       <c r="C112" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>643339915</v>
+        <v>215000</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>643m</t>
+          <t>215k</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G112" s="7" t="n">
-        <v>625</v>
+        <v>555</v>
       </c>
       <c r="H112" s="5" t="n">
         <v>3</v>
@@ -4906,10 +4914,10 @@
         <v>283</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K112" s="8" t="n">
-        <v>6135</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="113" ht="19" customHeight="1">
@@ -4917,24 +4925,24 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="n">
-        <v>112</v>
+        <v>168</v>
       </c>
       <c r="C113" s="6" t="n">
-        <v>1.06</v>
+        <v>1.014</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>681940310</v>
+        <v>218000</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>681m</t>
+          <t>218k</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G113" s="7" t="n">
-        <v>630</v>
+        <v>560</v>
       </c>
       <c r="H113" s="5" t="n">
         <v>3</v>
@@ -4943,10 +4951,10 @@
         <v>286</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K113" s="8" t="n">
-        <v>6220</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="114" ht="19" customHeight="1">
@@ -4954,24 +4962,24 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="n">
-        <v>113</v>
+        <v>169.5</v>
       </c>
       <c r="C114" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>722856729</v>
+        <v>220000</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>722m</t>
+          <t>220k</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>635</v>
+        <v>565</v>
       </c>
       <c r="H114" s="5" t="n">
         <v>3</v>
@@ -4980,10 +4988,10 @@
         <v>289</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K114" s="8" t="n">
-        <v>6305</v>
+        <v>3670</v>
       </c>
     </row>
     <row r="115" ht="19" customHeight="1">
@@ -4991,24 +4999,24 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="C115" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>766228133</v>
+        <v>222000</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>766m</t>
+          <t>222k</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G115" s="7" t="n">
-        <v>640</v>
+        <v>570</v>
       </c>
       <c r="H115" s="5" t="n">
         <v>3</v>
@@ -5017,10 +5025,10 @@
         <v>292</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K115" s="8" t="n">
-        <v>6390</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="116" ht="19" customHeight="1">
@@ -5028,24 +5036,24 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="n">
-        <v>115</v>
+        <v>172.5</v>
       </c>
       <c r="C116" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>812201821</v>
+        <v>224000</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>812m</t>
+          <t>224k</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G116" s="7" t="n">
-        <v>645</v>
+        <v>575</v>
       </c>
       <c r="H116" s="5" t="n">
         <v>3</v>
@@ -5054,10 +5062,10 @@
         <v>295</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K116" s="8" t="n">
-        <v>6475</v>
+        <v>3770</v>
       </c>
     </row>
     <row r="117" ht="19" customHeight="1">
@@ -5065,24 +5073,24 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="n">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="C117" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>860933930</v>
+        <v>226000</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>860m</t>
+          <t>226k</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G117" s="7" t="n">
-        <v>650</v>
+        <v>580</v>
       </c>
       <c r="H117" s="5" t="n">
         <v>3</v>
@@ -5091,10 +5099,10 @@
         <v>298</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K117" s="8" t="n">
-        <v>6560</v>
+        <v>3820</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -5102,24 +5110,24 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="n">
-        <v>117</v>
+        <v>175.5</v>
       </c>
       <c r="C118" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D118" s="8" t="n">
-        <v>912589966</v>
+        <v>228000</v>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>912m</t>
+          <t>228k</t>
         </is>
       </c>
       <c r="F118" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G118" s="7" t="n">
-        <v>655</v>
+        <v>585</v>
       </c>
       <c r="H118" s="5" t="n">
         <v>3</v>
@@ -5128,10 +5136,10 @@
         <v>301</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K118" s="8" t="n">
-        <v>6645</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="119" ht="19" customHeight="1">
@@ -5139,24 +5147,24 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="n">
-        <v>118</v>
+        <v>177</v>
       </c>
       <c r="C119" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D119" s="8" t="n">
-        <v>967345364</v>
+        <v>230000</v>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>967m</t>
+          <t>230k</t>
         </is>
       </c>
       <c r="F119" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G119" s="7" t="n">
-        <v>660</v>
+        <v>590</v>
       </c>
       <c r="H119" s="5" t="n">
         <v>3</v>
@@ -5165,10 +5173,10 @@
         <v>304</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K119" s="8" t="n">
-        <v>6730</v>
+        <v>3920</v>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
@@ -5176,24 +5184,24 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="n">
-        <v>119</v>
+        <v>178.5</v>
       </c>
       <c r="C120" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D120" s="8" t="n">
-        <v>1025386086</v>
+        <v>232000</v>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>1.02b</t>
+          <t>232k</t>
         </is>
       </c>
       <c r="F120" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>665</v>
+        <v>595</v>
       </c>
       <c r="H120" s="5" t="n">
         <v>3</v>
@@ -5202,10 +5210,10 @@
         <v>307</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K120" s="8" t="n">
-        <v>6815</v>
+        <v>3970</v>
       </c>
     </row>
     <row r="121" ht="19" customHeight="1">
@@ -5213,24 +5221,24 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="n">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C121" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0129</v>
       </c>
       <c r="D121" s="8" t="n">
-        <v>1086909251</v>
+        <v>235000</v>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>1.08b</t>
+          <t>235k</t>
         </is>
       </c>
       <c r="F121" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>670</v>
+        <v>600</v>
       </c>
       <c r="H121" s="5" t="n">
         <v>3</v>
@@ -5239,10 +5247,10 @@
         <v>310</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="K121" s="8" t="n">
-        <v>6900</v>
+        <v>4020</v>
       </c>
     </row>
     <row r="122" ht="19" customHeight="1">
@@ -5250,24 +5258,24 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="n">
-        <v>121</v>
+        <v>181.5</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D122" s="8" t="n">
-        <v>1152123806</v>
+        <v>237000</v>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>1.15b</t>
+          <t>237k</t>
         </is>
       </c>
       <c r="F122" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>675</v>
+        <v>605</v>
       </c>
       <c r="H122" s="5" t="n">
         <v>3</v>
@@ -5276,10 +5284,10 @@
         <v>313</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K122" s="8" t="n">
-        <v>6990</v>
+        <v>4073</v>
       </c>
     </row>
     <row r="123" ht="19" customHeight="1">
@@ -5287,24 +5295,24 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="n">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="C123" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D123" s="8" t="n">
-        <v>1221251234</v>
+        <v>239000</v>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>1.22b</t>
+          <t>239k</t>
         </is>
       </c>
       <c r="F123" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>680</v>
+        <v>610</v>
       </c>
       <c r="H123" s="5" t="n">
         <v>3</v>
@@ -5313,10 +5321,10 @@
         <v>316</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K123" s="8" t="n">
-        <v>7080</v>
+        <v>4126</v>
       </c>
     </row>
     <row r="124" ht="19" customHeight="1">
@@ -5324,24 +5332,24 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="n">
-        <v>123</v>
+        <v>184.5</v>
       </c>
       <c r="C124" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>1294526308</v>
+        <v>241000</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>1.29b</t>
+          <t>241k</t>
         </is>
       </c>
       <c r="F124" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>685</v>
+        <v>615</v>
       </c>
       <c r="H124" s="5" t="n">
         <v>3</v>
@@ -5350,10 +5358,10 @@
         <v>319</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K124" s="8" t="n">
-        <v>7170</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="125" ht="19" customHeight="1">
@@ -5361,24 +5369,24 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="n">
-        <v>124</v>
+        <v>186</v>
       </c>
       <c r="C125" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>1372197886</v>
+        <v>243000</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>1.37b</t>
+          <t>243k</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>690</v>
+        <v>620</v>
       </c>
       <c r="H125" s="5" t="n">
         <v>3</v>
@@ -5387,10 +5395,10 @@
         <v>322</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K125" s="8" t="n">
-        <v>7260</v>
+        <v>4232</v>
       </c>
     </row>
     <row r="126" ht="19" customHeight="1">
@@ -5398,24 +5406,24 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="n">
-        <v>125</v>
+        <v>187.5</v>
       </c>
       <c r="C126" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>1454529759</v>
+        <v>245000</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>1.45b</t>
+          <t>245k</t>
         </is>
       </c>
       <c r="F126" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>695</v>
+        <v>625</v>
       </c>
       <c r="H126" s="5" t="n">
         <v>3</v>
@@ -5424,10 +5432,10 @@
         <v>325</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K126" s="8" t="n">
-        <v>7350</v>
+        <v>4285</v>
       </c>
     </row>
     <row r="127" ht="19" customHeight="1">
@@ -5435,24 +5443,24 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="n">
-        <v>126</v>
+        <v>189</v>
       </c>
       <c r="C127" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D127" s="8" t="n">
-        <v>1541801545</v>
+        <v>247000</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>1.54b</t>
+          <t>247k</t>
         </is>
       </c>
       <c r="F127" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="H127" s="5" t="n">
         <v>3</v>
@@ -5461,10 +5469,10 @@
         <v>328</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K127" s="8" t="n">
-        <v>7440</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="128" ht="19" customHeight="1">
@@ -5472,24 +5480,24 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="n">
-        <v>127</v>
+        <v>190.5</v>
       </c>
       <c r="C128" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0121</v>
       </c>
       <c r="D128" s="8" t="n">
-        <v>1634309638</v>
+        <v>250000</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>1.63b</t>
+          <t>250k</t>
         </is>
       </c>
       <c r="F128" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>705</v>
+        <v>635</v>
       </c>
       <c r="H128" s="5" t="n">
         <v>3</v>
@@ -5498,10 +5506,10 @@
         <v>331</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K128" s="8" t="n">
-        <v>7530</v>
+        <v>4391</v>
       </c>
     </row>
     <row r="129" ht="19" customHeight="1">
@@ -5509,24 +5517,24 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="n">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="C129" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>1732368216</v>
+        <v>252000</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>1.73b</t>
+          <t>252k</t>
         </is>
       </c>
       <c r="F129" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G129" s="7" t="n">
-        <v>710</v>
+        <v>640</v>
       </c>
       <c r="H129" s="5" t="n">
         <v>3</v>
@@ -5535,10 +5543,10 @@
         <v>334</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K129" s="8" t="n">
-        <v>7620</v>
+        <v>4444</v>
       </c>
     </row>
     <row r="130" ht="19" customHeight="1">
@@ -5546,24 +5554,24 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="n">
-        <v>129</v>
+        <v>193.5</v>
       </c>
       <c r="C130" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D130" s="8" t="n">
-        <v>1836310309</v>
+        <v>254000</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>1.83b</t>
+          <t>254k</t>
         </is>
       </c>
       <c r="F130" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G130" s="7" t="n">
-        <v>715</v>
+        <v>645</v>
       </c>
       <c r="H130" s="5" t="n">
         <v>3</v>
@@ -5572,10 +5580,10 @@
         <v>337</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K130" s="8" t="n">
-        <v>7710</v>
+        <v>4497</v>
       </c>
     </row>
     <row r="131" ht="19" customHeight="1">
@@ -5583,24 +5591,24 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="n">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="C131" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D131" s="8" t="n">
-        <v>1946488928</v>
+        <v>256000</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>1.94b</t>
+          <t>256k</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G131" s="7" t="n">
-        <v>720</v>
+        <v>650</v>
       </c>
       <c r="H131" s="5" t="n">
         <v>3</v>
@@ -5609,10 +5617,10 @@
         <v>340</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K131" s="8" t="n">
-        <v>7800</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="132" ht="19" customHeight="1">
@@ -5620,24 +5628,24 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="n">
-        <v>131</v>
+        <v>196.5</v>
       </c>
       <c r="C132" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D132" s="8" t="n">
-        <v>2063278264</v>
+        <v>258000</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>2.06b</t>
+          <t>258k</t>
         </is>
       </c>
       <c r="F132" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>725</v>
+        <v>655</v>
       </c>
       <c r="H132" s="5" t="n">
         <v>3</v>
@@ -5646,10 +5654,10 @@
         <v>343</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K132" s="8" t="n">
-        <v>7895</v>
+        <v>4606</v>
       </c>
     </row>
     <row r="133" ht="19" customHeight="1">
@@ -5657,24 +5665,24 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="n">
-        <v>132</v>
+        <v>198</v>
       </c>
       <c r="C133" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>2187074960</v>
+        <v>260000</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>2.18b</t>
+          <t>260k</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G133" s="7" t="n">
-        <v>730</v>
+        <v>660</v>
       </c>
       <c r="H133" s="5" t="n">
         <v>3</v>
@@ -5683,10 +5691,10 @@
         <v>346</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K133" s="8" t="n">
-        <v>7990</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
@@ -5694,24 +5702,24 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="n">
-        <v>133</v>
+        <v>199.5</v>
       </c>
       <c r="C134" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D134" s="8" t="n">
-        <v>2318299458</v>
+        <v>262000</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>2.31b</t>
+          <t>262k</t>
         </is>
       </c>
       <c r="F134" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>735</v>
+        <v>665</v>
       </c>
       <c r="H134" s="5" t="n">
         <v>3</v>
@@ -5720,10 +5728,10 @@
         <v>349</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K134" s="8" t="n">
-        <v>8085</v>
+        <v>4718</v>
       </c>
     </row>
     <row r="135" ht="19" customHeight="1">
@@ -5731,24 +5739,24 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="n">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="C135" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D135" s="8" t="n">
-        <v>2457397425</v>
+        <v>264000</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>2.45b</t>
+          <t>264k</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G135" s="7" t="n">
-        <v>740</v>
+        <v>670</v>
       </c>
       <c r="H135" s="5" t="n">
         <v>3</v>
@@ -5757,10 +5765,10 @@
         <v>352</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K135" s="8" t="n">
-        <v>8180</v>
+        <v>4774</v>
       </c>
     </row>
     <row r="136" ht="19" customHeight="1">
@@ -5768,24 +5776,24 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="n">
-        <v>135</v>
+        <v>202.5</v>
       </c>
       <c r="C136" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0114</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>2604841270</v>
+        <v>267000</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>2.6b</t>
+          <t>267k</t>
         </is>
       </c>
       <c r="F136" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>745</v>
+        <v>675</v>
       </c>
       <c r="H136" s="5" t="n">
         <v>3</v>
@@ -5794,10 +5802,10 @@
         <v>355</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K136" s="8" t="n">
-        <v>8275</v>
+        <v>4830</v>
       </c>
     </row>
     <row r="137" ht="19" customHeight="1">
@@ -5805,24 +5813,24 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="n">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="C137" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>2761131746</v>
+        <v>269000</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>2.76b</t>
+          <t>269k</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="H137" s="5" t="n">
         <v>3</v>
@@ -5831,10 +5839,10 @@
         <v>358</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K137" s="8" t="n">
-        <v>8370</v>
+        <v>4886</v>
       </c>
     </row>
     <row r="138" ht="19" customHeight="1">
@@ -5842,24 +5850,24 @@
         <v>137</v>
       </c>
       <c r="B138" s="7" t="n">
-        <v>137</v>
+        <v>205.5</v>
       </c>
       <c r="C138" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D138" s="8" t="n">
-        <v>2926799651</v>
+        <v>271000</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>2.92b</t>
+          <t>271k</t>
         </is>
       </c>
       <c r="F138" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>755</v>
+        <v>685</v>
       </c>
       <c r="H138" s="5" t="n">
         <v>3</v>
@@ -5868,10 +5876,10 @@
         <v>361</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K138" s="8" t="n">
-        <v>8465</v>
+        <v>4942</v>
       </c>
     </row>
     <row r="139" ht="19" customHeight="1">
@@ -5879,24 +5887,24 @@
         <v>138</v>
       </c>
       <c r="B139" s="7" t="n">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="C139" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>3102407630</v>
+        <v>273000</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>3.1b</t>
+          <t>273k</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>760</v>
+        <v>690</v>
       </c>
       <c r="H139" s="5" t="n">
         <v>3</v>
@@ -5905,10 +5913,10 @@
         <v>364</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K139" s="8" t="n">
-        <v>8560</v>
+        <v>4998</v>
       </c>
     </row>
     <row r="140" ht="19" customHeight="1">
@@ -5916,24 +5924,24 @@
         <v>139</v>
       </c>
       <c r="B140" s="7" t="n">
-        <v>139</v>
+        <v>208.5</v>
       </c>
       <c r="C140" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D140" s="8" t="n">
-        <v>3288552088</v>
+        <v>275000</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>3.28b</t>
+          <t>275k</t>
         </is>
       </c>
       <c r="F140" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G140" s="7" t="n">
-        <v>765</v>
+        <v>695</v>
       </c>
       <c r="H140" s="5" t="n">
         <v>3</v>
@@ -5942,10 +5950,10 @@
         <v>367</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K140" s="8" t="n">
-        <v>8655</v>
+        <v>5054</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -5953,24 +5961,24 @@
         <v>140</v>
       </c>
       <c r="B141" s="7" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="C141" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D141" s="8" t="n">
-        <v>3485865213</v>
+        <v>277000</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>3.48b</t>
+          <t>277k</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>770</v>
+        <v>700</v>
       </c>
       <c r="H141" s="5" t="n">
         <v>3</v>
@@ -5979,10 +5987,10 @@
         <v>370</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="K141" s="8" t="n">
-        <v>8750</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -5990,24 +5998,24 @@
         <v>141</v>
       </c>
       <c r="B142" s="7" t="n">
-        <v>141</v>
+        <v>211.5</v>
       </c>
       <c r="C142" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D142" s="8" t="n">
-        <v>3695017126</v>
+        <v>279000</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>3.69b</t>
+          <t>279k</t>
         </is>
       </c>
       <c r="F142" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>775</v>
+        <v>705</v>
       </c>
       <c r="H142" s="5" t="n">
         <v>3</v>
@@ -6016,10 +6024,10 @@
         <v>373</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K142" s="8" t="n">
-        <v>8850</v>
+        <v>5169</v>
       </c>
     </row>
     <row r="143" ht="19" customHeight="1">
@@ -6027,24 +6035,24 @@
         <v>142</v>
       </c>
       <c r="B143" s="7" t="n">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="C143" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0108</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>3916718154</v>
+        <v>282000</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>3.91b</t>
+          <t>282k</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G143" s="7" t="n">
-        <v>780</v>
+        <v>710</v>
       </c>
       <c r="H143" s="5" t="n">
         <v>3</v>
@@ -6053,10 +6061,10 @@
         <v>376</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K143" s="8" t="n">
-        <v>8950</v>
+        <v>5228</v>
       </c>
     </row>
     <row r="144" ht="19" customHeight="1">
@@ -6064,24 +6072,24 @@
         <v>143</v>
       </c>
       <c r="B144" s="7" t="n">
-        <v>143</v>
+        <v>214.5</v>
       </c>
       <c r="C144" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D144" s="8" t="n">
-        <v>4151721243</v>
+        <v>284000</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>4.15b</t>
+          <t>284k</t>
         </is>
       </c>
       <c r="F144" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G144" s="7" t="n">
-        <v>785</v>
+        <v>715</v>
       </c>
       <c r="H144" s="5" t="n">
         <v>3</v>
@@ -6090,10 +6098,10 @@
         <v>379</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K144" s="8" t="n">
-        <v>9050</v>
+        <v>5287</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1">
@@ -6101,24 +6109,24 @@
         <v>144</v>
       </c>
       <c r="B145" s="7" t="n">
-        <v>144</v>
+        <v>216</v>
       </c>
       <c r="C145" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D145" s="8" t="n">
-        <v>4400824518</v>
+        <v>286000</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>4.4b</t>
+          <t>286k</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G145" s="7" t="n">
-        <v>790</v>
+        <v>720</v>
       </c>
       <c r="H145" s="5" t="n">
         <v>3</v>
@@ -6127,10 +6135,10 @@
         <v>382</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K145" s="8" t="n">
-        <v>9150</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="146" ht="19" customHeight="1">
@@ -6138,24 +6146,24 @@
         <v>145</v>
       </c>
       <c r="B146" s="7" t="n">
-        <v>145</v>
+        <v>217.5</v>
       </c>
       <c r="C146" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D146" s="8" t="n">
-        <v>4664873989</v>
+        <v>288000</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>4.66b</t>
+          <t>288k</t>
         </is>
       </c>
       <c r="F146" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G146" s="7" t="n">
-        <v>795</v>
+        <v>725</v>
       </c>
       <c r="H146" s="5" t="n">
         <v>3</v>
@@ -6164,10 +6172,10 @@
         <v>385</v>
       </c>
       <c r="J146" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K146" s="8" t="n">
-        <v>9250</v>
+        <v>5405</v>
       </c>
     </row>
     <row r="147" ht="19" customHeight="1">
@@ -6175,24 +6183,24 @@
         <v>146</v>
       </c>
       <c r="B147" s="7" t="n">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="C147" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D147" s="8" t="n">
-        <v>4944766428</v>
+        <v>290000</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>4.94b</t>
+          <t>290k</t>
         </is>
       </c>
       <c r="F147" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G147" s="7" t="n">
-        <v>800</v>
+        <v>730</v>
       </c>
       <c r="H147" s="5" t="n">
         <v>3</v>
@@ -6201,10 +6209,10 @@
         <v>388</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K147" s="8" t="n">
-        <v>9350</v>
+        <v>5464</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -6212,24 +6220,24 @@
         <v>147</v>
       </c>
       <c r="B148" s="7" t="n">
-        <v>147</v>
+        <v>220.5</v>
       </c>
       <c r="C148" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D148" s="8" t="n">
-        <v>5241452414</v>
+        <v>292000</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>5.24b</t>
+          <t>292k</t>
         </is>
       </c>
       <c r="F148" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>805</v>
+        <v>735</v>
       </c>
       <c r="H148" s="5" t="n">
         <v>3</v>
@@ -6238,10 +6246,10 @@
         <v>391</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K148" s="8" t="n">
-        <v>9450</v>
+        <v>5523</v>
       </c>
     </row>
     <row r="149" ht="19" customHeight="1">
@@ -6249,24 +6257,24 @@
         <v>148</v>
       </c>
       <c r="B149" s="7" t="n">
-        <v>148</v>
+        <v>222</v>
       </c>
       <c r="C149" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D149" s="8" t="n">
-        <v>5555939559</v>
+        <v>294000</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>5.55b</t>
+          <t>294k</t>
         </is>
       </c>
       <c r="F149" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G149" s="7" t="n">
-        <v>810</v>
+        <v>740</v>
       </c>
       <c r="H149" s="5" t="n">
         <v>3</v>
@@ -6275,10 +6283,10 @@
         <v>394</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K149" s="8" t="n">
-        <v>9550</v>
+        <v>5582</v>
       </c>
     </row>
     <row r="150" ht="19" customHeight="1">
@@ -6286,24 +6294,24 @@
         <v>149</v>
       </c>
       <c r="B150" s="7" t="n">
-        <v>149</v>
+        <v>223.5</v>
       </c>
       <c r="C150" s="6" t="n">
-        <v>1.06</v>
+        <v>1.0102</v>
       </c>
       <c r="D150" s="8" t="n">
-        <v>5889295933</v>
+        <v>297000</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>5.88b</t>
+          <t>297k</t>
         </is>
       </c>
       <c r="F150" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>815</v>
+        <v>745</v>
       </c>
       <c r="H150" s="5" t="n">
         <v>3</v>
@@ -6312,10 +6320,10 @@
         <v>397</v>
       </c>
       <c r="J150" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K150" s="8" t="n">
-        <v>9650</v>
+        <v>5641</v>
       </c>
     </row>
     <row r="151" ht="19" customHeight="1">
@@ -6323,24 +6331,24 @@
         <v>150</v>
       </c>
       <c r="B151" s="7" t="n">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="C151" s="6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="D151" s="8" t="n">
-        <v>6242653689</v>
+        <v>299000</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>6.24b</t>
+          <t>299k</t>
         </is>
       </c>
       <c r="F151" s="5" t="n">
         <v>5</v>
       </c>
       <c r="G151" s="7" t="n">
-        <v>820</v>
+        <v>750</v>
       </c>
       <c r="H151" s="5" t="n">
         <v>3</v>
@@ -6349,10 +6357,10 @@
         <v>400</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="K151" s="8" t="n">
-        <v>9750</v>
+        <v>5700</v>
       </c>
     </row>
   </sheetData>

--- a/Kachi_Gun/Table/Mission.xlsx
+++ b/Kachi_Gun/Table/Mission.xlsx
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="D2" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="D3" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         <v>1</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
@@ -881,10 +881,10 @@
         <v>2</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1">
@@ -895,14 +895,14 @@
         <v>4.5</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>1.6248</v>
+        <v>1.223</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>1100</v>
+        <v>828</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1.1k</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F4" s="5" t="n">
@@ -918,10 +918,10 @@
         <v>4</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1">
@@ -932,14 +932,14 @@
         <v>6</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>2.2091</v>
+        <v>2.3188</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>2430</v>
+        <v>1920</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2.43k</t>
+          <t>1.92k</t>
         </is>
       </c>
       <c r="F5" s="5" t="n">
@@ -955,10 +955,10 @@
         <v>6</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" ht="19" customHeight="1">
@@ -969,14 +969,14 @@
         <v>7.5</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2.1523</v>
+        <v>2.6094</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>5230</v>
+        <v>5010</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>5.23k</t>
+          <t>5.01k</t>
         </is>
       </c>
       <c r="F6" s="5" t="n">
@@ -992,10 +992,10 @@
         <v>9</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1">
@@ -1006,14 +1006,14 @@
         <v>9</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>1.6673</v>
+        <v>2.1158</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>8720</v>
+        <v>10600</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>8.72k</t>
+          <t>10.6k</t>
         </is>
       </c>
       <c r="F7" s="5" t="n">
@@ -1029,10 +1029,10 @@
         <v>12</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1">
@@ -1043,14 +1043,14 @@
         <v>10.5</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>1.3761</v>
+        <v>1.283</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>12000</v>
+        <v>13600</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>12k</t>
+          <t>13.6k</t>
         </is>
       </c>
       <c r="F8" s="5" t="n">
@@ -1066,10 +1066,10 @@
         <v>14</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1">
@@ -1080,14 +1080,14 @@
         <v>12</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>1.325</v>
+        <v>1.2059</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>15900</v>
+        <v>16400</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>15.9k</t>
+          <t>16.4k</t>
         </is>
       </c>
       <c r="F9" s="5" t="n">
@@ -1103,10 +1103,10 @@
         <v>16</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>136</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
@@ -1117,14 +1117,14 @@
         <v>13.5</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1.1635</v>
+        <v>1.1098</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>18500</v>
+        <v>18200</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>18.5k</t>
+          <t>18.2k</t>
         </is>
       </c>
       <c r="F10" s="5" t="n">
@@ -1140,10 +1140,10 @@
         <v>18</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>153</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
@@ -1154,14 +1154,14 @@
         <v>15</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1.173</v>
+        <v>1.1154</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>21700</v>
+        <v>20300</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>21.7k</t>
+          <t>20.3k</t>
         </is>
       </c>
       <c r="F11" s="5" t="n">
@@ -1177,10 +1177,10 @@
         <v>20</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>170</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
@@ -1191,14 +1191,14 @@
         <v>16.5</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>1.129</v>
+        <v>1.1724</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>24500</v>
+        <v>23800</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>24.5k</t>
+          <t>23.8k</t>
         </is>
       </c>
       <c r="F12" s="5" t="n">
@@ -1214,10 +1214,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>190</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
@@ -1228,14 +1228,14 @@
         <v>18</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>1.1388</v>
+        <v>1.0882</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>27900</v>
+        <v>25900</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>27.9k</t>
+          <t>25.9k</t>
         </is>
       </c>
       <c r="F13" s="5" t="n">
@@ -1251,10 +1251,10 @@
         <v>24</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>210</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1265,14 +1265,14 @@
         <v>19.5</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1.0753</v>
+        <v>1.0965</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>30000</v>
+        <v>28400</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>30k</t>
+          <t>28.4k</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -1288,10 +1288,10 @@
         <v>26</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>230</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
@@ -1302,14 +1302,14 @@
         <v>21</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1.0533</v>
+        <v>1.081</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>31600</v>
+        <v>30700</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>31.6k</t>
+          <t>30.7k</t>
         </is>
       </c>
       <c r="F15" s="5" t="n">
@@ -1325,10 +1325,10 @@
         <v>28</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>250</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
@@ -1339,14 +1339,14 @@
         <v>22.5</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>1.1203</v>
+        <v>1.127</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>35400</v>
+        <v>34600</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>35.4k</t>
+          <t>34.6k</t>
         </is>
       </c>
       <c r="F16" s="5" t="n">
@@ -1362,10 +1362,10 @@
         <v>30</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>270</v>
+        <v>410</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
@@ -1376,14 +1376,14 @@
         <v>24</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1.0621</v>
+        <v>1.0636</v>
       </c>
       <c r="D17" s="8" t="n">
-        <v>37600</v>
+        <v>36800</v>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>37.6k</t>
+          <t>36.8k</t>
         </is>
       </c>
       <c r="F17" s="5" t="n">
@@ -1399,10 +1399,10 @@
         <v>32</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>290</v>
+        <v>440</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
@@ -1413,14 +1413,14 @@
         <v>25.5</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1.0638</v>
+        <v>1.0842</v>
       </c>
       <c r="D18" s="8" t="n">
-        <v>40000</v>
+        <v>39900</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>40k</t>
+          <t>39.9k</t>
         </is>
       </c>
       <c r="F18" s="5" t="n">
@@ -1436,10 +1436,10 @@
         <v>34</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>310</v>
+        <v>470</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
@@ -1450,14 +1450,14 @@
         <v>27</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>1.05</v>
+        <v>1.0802</v>
       </c>
       <c r="D19" s="8" t="n">
-        <v>42000</v>
+        <v>43100</v>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>42k</t>
+          <t>43.1k</t>
         </is>
       </c>
       <c r="F19" s="5" t="n">
@@ -1473,10 +1473,10 @@
         <v>36</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>330</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
@@ -1487,14 +1487,14 @@
         <v>28.5</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>1.0571</v>
+        <v>1.0139</v>
       </c>
       <c r="D20" s="8" t="n">
-        <v>44400</v>
+        <v>43700</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>44.4k</t>
+          <t>43.7k</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
@@ -1510,10 +1510,10 @@
         <v>38</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>350</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
@@ -1524,14 +1524,14 @@
         <v>30</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>1.0315</v>
+        <v>1.0595</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>45800</v>
+        <v>46300</v>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>45.8k</t>
+          <t>46.3k</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
@@ -1547,10 +1547,10 @@
         <v>40</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>370</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
@@ -1561,14 +1561,14 @@
         <v>31.5</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>1.0371</v>
+        <v>1.0324</v>
       </c>
       <c r="D22" s="8" t="n">
-        <v>47500</v>
+        <v>47800</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>47.5k</t>
+          <t>47.8k</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
@@ -1584,10 +1584,10 @@
         <v>42</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>393</v>
+        <v>594</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
@@ -1598,14 +1598,14 @@
         <v>33</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>1.0505</v>
+        <v>1.0314</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>49900</v>
+        <v>49300</v>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>49.9k</t>
+          <t>49.3k</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
@@ -1621,10 +1621,10 @@
         <v>44</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>416</v>
+        <v>628</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
@@ -1635,7 +1635,7 @@
         <v>34.5</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>1.0301</v>
+        <v>1.0426</v>
       </c>
       <c r="D24" s="8" t="n">
         <v>51400</v>
@@ -1658,10 +1658,10 @@
         <v>46</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>439</v>
+        <v>662</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
@@ -1672,14 +1672,14 @@
         <v>36</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>1.0272</v>
+        <v>1.0175</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>52800</v>
+        <v>52300</v>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>52.8k</t>
+          <t>52.3k</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -1695,10 +1695,10 @@
         <v>48</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>462</v>
+        <v>696</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
@@ -1709,14 +1709,14 @@
         <v>37.5</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>1.036</v>
+        <v>1.0325</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>54700</v>
+        <v>54000</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>54.7k</t>
+          <t>54k</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
@@ -1732,10 +1732,10 @@
         <v>50</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>485</v>
+        <v>730</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
@@ -1746,14 +1746,14 @@
         <v>39</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>1.0146</v>
+        <v>1.0333</v>
       </c>
       <c r="D27" s="8" t="n">
-        <v>55500</v>
+        <v>55800</v>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>55.5k</t>
+          <t>55.8k</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -1769,10 +1769,10 @@
         <v>52</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>508</v>
+        <v>764</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
@@ -1783,14 +1783,14 @@
         <v>40.5</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>1.036</v>
+        <v>1.0466</v>
       </c>
       <c r="D28" s="8" t="n">
-        <v>57500</v>
+        <v>58400</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>57.5k</t>
+          <t>58.4k</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
@@ -1806,10 +1806,10 @@
         <v>54</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>531</v>
+        <v>798</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
@@ -1820,14 +1820,14 @@
         <v>42</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>1.0174</v>
+        <v>1.0223</v>
       </c>
       <c r="D29" s="8" t="n">
-        <v>58500</v>
+        <v>59700</v>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>58.5k</t>
+          <t>59.7k</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
@@ -1843,10 +1843,10 @@
         <v>56</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>554</v>
+        <v>832</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
@@ -1857,14 +1857,14 @@
         <v>43.5</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>1.0376</v>
+        <v>1.0235</v>
       </c>
       <c r="D30" s="8" t="n">
-        <v>60700</v>
+        <v>61100</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>60.7k</t>
+          <t>61.1k</t>
         </is>
       </c>
       <c r="F30" s="5" t="n">
@@ -1880,10 +1880,10 @@
         <v>58</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K30" s="8" t="n">
-        <v>577</v>
+        <v>866</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
@@ -1894,14 +1894,14 @@
         <v>45</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1.0132</v>
+        <v>1.0147</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>61500</v>
+        <v>62000</v>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>61.5k</t>
+          <t>62k</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -1917,10 +1917,10 @@
         <v>60</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K31" s="8" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
@@ -1931,14 +1931,14 @@
         <v>46.5</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>1.039</v>
+        <v>1.0113</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>63900</v>
+        <v>62700</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>63.9k</t>
+          <t>62.7k</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -1954,10 +1954,10 @@
         <v>62</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K32" s="8" t="n">
-        <v>626</v>
+        <v>938</v>
       </c>
     </row>
     <row r="33" ht="19" customHeight="1">
@@ -1968,14 +1968,14 @@
         <v>48</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>1.0188</v>
+        <v>1.0239</v>
       </c>
       <c r="D33" s="8" t="n">
-        <v>65100</v>
+        <v>64200</v>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>65.1k</t>
+          <t>64.2k</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
@@ -1991,10 +1991,10 @@
         <v>64</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>652</v>
+        <v>976</v>
       </c>
     </row>
     <row r="34" ht="19" customHeight="1">
@@ -2005,14 +2005,14 @@
         <v>49.5</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>1.0108</v>
+        <v>1.01</v>
       </c>
       <c r="D34" s="8" t="n">
-        <v>65800</v>
+        <v>64400</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>65.8k</t>
+          <t>64.4k</t>
         </is>
       </c>
       <c r="F34" s="5" t="n">
@@ -2028,10 +2028,10 @@
         <v>66</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K34" s="8" t="n">
-        <v>678</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
@@ -2042,14 +2042,14 @@
         <v>51</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>1.0304</v>
+        <v>1.01</v>
       </c>
       <c r="D35" s="8" t="n">
-        <v>67800</v>
+        <v>64500</v>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>67.8k</t>
+          <t>64.5k</t>
         </is>
       </c>
       <c r="F35" s="5" t="n">
@@ -2065,10 +2065,10 @@
         <v>68</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K35" s="8" t="n">
-        <v>704</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="36" ht="19" customHeight="1">
@@ -2082,11 +2082,11 @@
         <v>1.01</v>
       </c>
       <c r="D36" s="8" t="n">
-        <v>68200</v>
+        <v>65000</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>68.2k</t>
+          <t>65k</t>
         </is>
       </c>
       <c r="F36" s="5" t="n">
@@ -2102,10 +2102,10 @@
         <v>70</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K36" s="8" t="n">
-        <v>730</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
@@ -2116,14 +2116,14 @@
         <v>54</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>1.0279</v>
+        <v>1.0246</v>
       </c>
       <c r="D37" s="8" t="n">
-        <v>70100</v>
+        <v>66600</v>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>70.1k</t>
+          <t>66.6k</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
@@ -2139,10 +2139,10 @@
         <v>72</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K37" s="8" t="n">
-        <v>756</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
@@ -2153,14 +2153,14 @@
         <v>55.5</v>
       </c>
       <c r="C38" s="6" t="n">
-        <v>1.0214</v>
+        <v>1.01</v>
       </c>
       <c r="D38" s="8" t="n">
-        <v>71600</v>
+        <v>66800</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>71.6k</t>
+          <t>66.8k</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
@@ -2176,10 +2176,10 @@
         <v>74</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K38" s="8" t="n">
-        <v>782</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
@@ -2190,14 +2190,14 @@
         <v>57</v>
       </c>
       <c r="C39" s="6" t="n">
-        <v>1.0363</v>
+        <v>1.018</v>
       </c>
       <c r="D39" s="8" t="n">
-        <v>74200</v>
+        <v>68000</v>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>74.2k</t>
+          <t>68k</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
@@ -2213,10 +2213,10 @@
         <v>76</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K39" s="8" t="n">
-        <v>808</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
@@ -2227,14 +2227,14 @@
         <v>58.5</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0265</v>
       </c>
       <c r="D40" s="8" t="n">
-        <v>74300</v>
+        <v>69800</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>74.3k</t>
+          <t>69.8k</t>
         </is>
       </c>
       <c r="F40" s="5" t="n">
@@ -2250,10 +2250,10 @@
         <v>78</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K40" s="8" t="n">
-        <v>834</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
@@ -2264,14 +2264,14 @@
         <v>60</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0143</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>74500</v>
+        <v>70800</v>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>74.5k</t>
+          <t>70.8k</t>
         </is>
       </c>
       <c r="F41" s="5" t="n">
@@ -2287,10 +2287,10 @@
         <v>80</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K41" s="8" t="n">
-        <v>860</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
@@ -2301,14 +2301,14 @@
         <v>61.5</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1.0134</v>
+        <v>1.01</v>
       </c>
       <c r="D42" s="8" t="n">
-        <v>75500</v>
+        <v>70900</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>75.5k</t>
+          <t>70.9k</t>
         </is>
       </c>
       <c r="F42" s="5" t="n">
@@ -2324,10 +2324,10 @@
         <v>82</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K42" s="8" t="n">
-        <v>889</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
@@ -2338,14 +2338,14 @@
         <v>63</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>1.0106</v>
+        <v>1.01</v>
       </c>
       <c r="D43" s="8" t="n">
-        <v>76300</v>
+        <v>71100</v>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>76.3k</t>
+          <t>71.1k</t>
         </is>
       </c>
       <c r="F43" s="5" t="n">
@@ -2361,10 +2361,10 @@
         <v>84</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K43" s="8" t="n">
-        <v>918</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
@@ -2375,14 +2375,14 @@
         <v>64.5</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1.0157</v>
+        <v>1.0197</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>77500</v>
+        <v>72500</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>77.5k</t>
+          <t>72.5k</t>
         </is>
       </c>
       <c r="F44" s="5" t="n">
@@ -2398,10 +2398,10 @@
         <v>86</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K44" s="8" t="n">
-        <v>947</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
@@ -2412,14 +2412,14 @@
         <v>66</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1.0116</v>
+        <v>1.01</v>
       </c>
       <c r="D45" s="8" t="n">
-        <v>78400</v>
+        <v>72800</v>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>78.4k</t>
+          <t>72.8k</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
@@ -2435,10 +2435,10 @@
         <v>88</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K45" s="8" t="n">
-        <v>976</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
@@ -2449,14 +2449,14 @@
         <v>67.5</v>
       </c>
       <c r="C46" s="6" t="n">
-        <v>1.0217</v>
+        <v>1.01</v>
       </c>
       <c r="D46" s="8" t="n">
-        <v>80100</v>
+        <v>73400</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>80.1k</t>
+          <t>73.4k</t>
         </is>
       </c>
       <c r="F46" s="5" t="n">
@@ -2472,10 +2472,10 @@
         <v>90</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K46" s="8" t="n">
-        <v>1005</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
@@ -2486,14 +2486,14 @@
         <v>69</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1.0175</v>
+        <v>1.015</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>81500</v>
+        <v>74500</v>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>81.5k</t>
+          <t>74.5k</t>
         </is>
       </c>
       <c r="F47" s="5" t="n">
@@ -2509,10 +2509,10 @@
         <v>92</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K47" s="8" t="n">
-        <v>1034</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
@@ -2523,14 +2523,14 @@
         <v>70.5</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0188</v>
       </c>
       <c r="D48" s="8" t="n">
-        <v>81600</v>
+        <v>75900</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>81.6k</t>
+          <t>75.9k</t>
         </is>
       </c>
       <c r="F48" s="5" t="n">
@@ -2546,10 +2546,10 @@
         <v>94</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K48" s="8" t="n">
-        <v>1063</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
@@ -2563,11 +2563,11 @@
         <v>1.01</v>
       </c>
       <c r="D49" s="8" t="n">
-        <v>81800</v>
+        <v>76600</v>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>81.8k</t>
+          <t>76.6k</t>
         </is>
       </c>
       <c r="F49" s="5" t="n">
@@ -2583,10 +2583,10 @@
         <v>96</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K49" s="8" t="n">
-        <v>1092</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
@@ -2597,14 +2597,14 @@
         <v>73.5</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>1.0147</v>
+        <v>1.0222</v>
       </c>
       <c r="D50" s="8" t="n">
-        <v>83000</v>
+        <v>78300</v>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>83k</t>
+          <t>78.3k</t>
         </is>
       </c>
       <c r="F50" s="5" t="n">
@@ -2620,10 +2620,10 @@
         <v>98</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K50" s="8" t="n">
-        <v>1121</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
@@ -2634,14 +2634,14 @@
         <v>75</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0294</v>
       </c>
       <c r="D51" s="8" t="n">
-        <v>83200</v>
+        <v>80600</v>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>83.2k</t>
+          <t>80.6k</t>
         </is>
       </c>
       <c r="F51" s="5" t="n">
@@ -2657,10 +2657,10 @@
         <v>100</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K51" s="8" t="n">
-        <v>1150</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
@@ -2671,14 +2671,14 @@
         <v>76.5</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>1.024</v>
+        <v>1.01</v>
       </c>
       <c r="D52" s="8" t="n">
-        <v>85200</v>
+        <v>80800</v>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>85.2k</t>
+          <t>80.8k</t>
         </is>
       </c>
       <c r="F52" s="5" t="n">
@@ -2694,10 +2694,10 @@
         <v>103</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K52" s="8" t="n">
-        <v>1182</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
@@ -2711,11 +2711,11 @@
         <v>1.01</v>
       </c>
       <c r="D53" s="8" t="n">
-        <v>86000</v>
+        <v>80900</v>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>86k</t>
+          <t>80.9k</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
@@ -2731,10 +2731,10 @@
         <v>106</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K53" s="8" t="n">
-        <v>1214</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
@@ -2745,14 +2745,14 @@
         <v>79.5</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>1.0233</v>
+        <v>1.0148</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>88000</v>
+        <v>82100</v>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>88k</t>
+          <t>82.1k</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
@@ -2768,10 +2768,10 @@
         <v>109</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K54" s="8" t="n">
-        <v>1246</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
@@ -2782,14 +2782,14 @@
         <v>81</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1.0432</v>
+        <v>1.0122</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>91800</v>
+        <v>83100</v>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>91.8k</t>
+          <t>83.1k</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
@@ -2805,10 +2805,10 @@
         <v>112</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K55" s="8" t="n">
-        <v>1278</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
@@ -2819,14 +2819,14 @@
         <v>82.5</v>
       </c>
       <c r="C56" s="6" t="n">
-        <v>1.0109</v>
+        <v>1.012</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>92800</v>
+        <v>84100</v>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>92.8k</t>
+          <t>84.1k</t>
         </is>
       </c>
       <c r="F56" s="5" t="n">
@@ -2842,10 +2842,10 @@
         <v>115</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K56" s="8" t="n">
-        <v>1310</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
@@ -2856,14 +2856,14 @@
         <v>84</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>1.0129</v>
+        <v>1.01</v>
       </c>
       <c r="D57" s="8" t="n">
-        <v>94000</v>
+        <v>84900</v>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>94k</t>
+          <t>84.9k</t>
         </is>
       </c>
       <c r="F57" s="5" t="n">
@@ -2879,10 +2879,10 @@
         <v>118</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K57" s="8" t="n">
-        <v>1342</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
@@ -2893,14 +2893,14 @@
         <v>85.5</v>
       </c>
       <c r="C58" s="6" t="n">
-        <v>1.0149</v>
+        <v>1.0236</v>
       </c>
       <c r="D58" s="8" t="n">
-        <v>95400</v>
+        <v>86900</v>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>95.4k</t>
+          <t>86.9k</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
@@ -2916,10 +2916,10 @@
         <v>121</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K58" s="8" t="n">
-        <v>1374</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
@@ -2930,14 +2930,14 @@
         <v>87</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>1.0136</v>
+        <v>1.0426</v>
       </c>
       <c r="D59" s="8" t="n">
-        <v>96700</v>
+        <v>90600</v>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>96.7k</t>
+          <t>90.6k</t>
         </is>
       </c>
       <c r="F59" s="5" t="n">
@@ -2953,10 +2953,10 @@
         <v>124</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K59" s="8" t="n">
-        <v>1406</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
@@ -2967,14 +2967,14 @@
         <v>88.5</v>
       </c>
       <c r="C60" s="6" t="n">
-        <v>1.0259</v>
+        <v>1.0519</v>
       </c>
       <c r="D60" s="8" t="n">
-        <v>99200</v>
+        <v>95300</v>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>99.2k</t>
+          <t>95.3k</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
@@ -2990,10 +2990,10 @@
         <v>127</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K60" s="8" t="n">
-        <v>1438</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
@@ -3004,14 +3004,14 @@
         <v>90</v>
       </c>
       <c r="C61" s="6" t="n">
-        <v>1.0181</v>
+        <v>1.0115</v>
       </c>
       <c r="D61" s="8" t="n">
-        <v>101000</v>
+        <v>96400</v>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>101k</t>
+          <t>96.4k</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
@@ -3027,10 +3027,10 @@
         <v>130</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="K61" s="8" t="n">
-        <v>1470</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="62" ht="19" customHeight="1">
@@ -3041,14 +3041,14 @@
         <v>91.5</v>
       </c>
       <c r="C62" s="6" t="n">
-        <v>1.0495</v>
+        <v>1.01</v>
       </c>
       <c r="D62" s="8" t="n">
-        <v>106000</v>
+        <v>97000</v>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>106k</t>
+          <t>97k</t>
         </is>
       </c>
       <c r="F62" s="5" t="n">
@@ -3064,10 +3064,10 @@
         <v>133</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K62" s="8" t="n">
-        <v>1505</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
@@ -3078,14 +3078,14 @@
         <v>93</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>1.0472</v>
+        <v>1.0278</v>
       </c>
       <c r="D63" s="8" t="n">
-        <v>111000</v>
+        <v>99700</v>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>111k</t>
+          <t>99.7k</t>
         </is>
       </c>
       <c r="F63" s="5" t="n">
@@ -3101,10 +3101,10 @@
         <v>136</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K63" s="8" t="n">
-        <v>1540</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="64" ht="19" customHeight="1">
@@ -3115,14 +3115,14 @@
         <v>94.5</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>1.018</v>
+        <v>1.0231</v>
       </c>
       <c r="D64" s="8" t="n">
-        <v>113000</v>
+        <v>102000</v>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>113k</t>
+          <t>102k</t>
         </is>
       </c>
       <c r="F64" s="5" t="n">
@@ -3138,10 +3138,10 @@
         <v>139</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K64" s="8" t="n">
-        <v>1575</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="65" ht="19" customHeight="1">
@@ -3152,14 +3152,14 @@
         <v>96</v>
       </c>
       <c r="C65" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0196</v>
       </c>
       <c r="D65" s="8" t="n">
-        <v>114000</v>
+        <v>104000</v>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>114k</t>
+          <t>104k</t>
         </is>
       </c>
       <c r="F65" s="5" t="n">
@@ -3175,10 +3175,10 @@
         <v>142</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K65" s="8" t="n">
-        <v>1610</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="66" ht="19" customHeight="1">
@@ -3189,14 +3189,14 @@
         <v>97.5</v>
       </c>
       <c r="C66" s="6" t="n">
-        <v>1.0175</v>
+        <v>1.0192</v>
       </c>
       <c r="D66" s="8" t="n">
-        <v>116000</v>
+        <v>106000</v>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>116k</t>
+          <t>106k</t>
         </is>
       </c>
       <c r="F66" s="5" t="n">
@@ -3212,10 +3212,10 @@
         <v>145</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K66" s="8" t="n">
-        <v>1645</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="67" ht="19" customHeight="1">
@@ -3226,14 +3226,14 @@
         <v>99</v>
       </c>
       <c r="C67" s="6" t="n">
-        <v>1.0259</v>
+        <v>1.0472</v>
       </c>
       <c r="D67" s="8" t="n">
-        <v>119000</v>
+        <v>111000</v>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>119k</t>
+          <t>111k</t>
         </is>
       </c>
       <c r="F67" s="5" t="n">
@@ -3249,10 +3249,10 @@
         <v>148</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K67" s="8" t="n">
-        <v>1680</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="68" ht="19" customHeight="1">
@@ -3263,14 +3263,14 @@
         <v>100.5</v>
       </c>
       <c r="C68" s="6" t="n">
-        <v>1.0504</v>
+        <v>1.0901</v>
       </c>
       <c r="D68" s="8" t="n">
-        <v>125000</v>
+        <v>121000</v>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>125k</t>
+          <t>121k</t>
         </is>
       </c>
       <c r="F68" s="5" t="n">
@@ -3286,10 +3286,10 @@
         <v>151</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K68" s="8" t="n">
-        <v>1715</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="69" ht="19" customHeight="1">
@@ -3300,14 +3300,14 @@
         <v>102</v>
       </c>
       <c r="C69" s="6" t="n">
-        <v>1.024</v>
+        <v>1.0496</v>
       </c>
       <c r="D69" s="8" t="n">
-        <v>128000</v>
+        <v>127000</v>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>128k</t>
+          <t>127k</t>
         </is>
       </c>
       <c r="F69" s="5" t="n">
@@ -3323,10 +3323,10 @@
         <v>154</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K69" s="8" t="n">
-        <v>1750</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="70" ht="19" customHeight="1">
@@ -3337,14 +3337,14 @@
         <v>103.5</v>
       </c>
       <c r="C70" s="6" t="n">
-        <v>1.0391</v>
+        <v>1.01</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>133000</v>
+        <v>127001</v>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>133k</t>
+          <t>127k</t>
         </is>
       </c>
       <c r="F70" s="5" t="n">
@@ -3360,10 +3360,10 @@
         <v>157</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K70" s="8" t="n">
-        <v>1785</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="71" ht="19" customHeight="1">
@@ -3374,14 +3374,14 @@
         <v>105</v>
       </c>
       <c r="C71" s="6" t="n">
-        <v>1.0451</v>
+        <v>1.01</v>
       </c>
       <c r="D71" s="8" t="n">
-        <v>139000</v>
+        <v>127002</v>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>139k</t>
+          <t>127k</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
@@ -3397,10 +3397,10 @@
         <v>160</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="K71" s="8" t="n">
-        <v>1820</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="72" ht="19" customHeight="1">
@@ -3411,14 +3411,14 @@
         <v>106.5</v>
       </c>
       <c r="C72" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0157</v>
       </c>
       <c r="D72" s="8" t="n">
-        <v>139001</v>
+        <v>129000</v>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>139k</t>
+          <t>129k</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
@@ -3434,10 +3434,10 @@
         <v>163</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K72" s="8" t="n">
-        <v>1858</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="73" ht="19" customHeight="1">
@@ -3451,11 +3451,11 @@
         <v>1.01</v>
       </c>
       <c r="D73" s="8" t="n">
-        <v>139002</v>
+        <v>130000</v>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>139k</t>
+          <t>130k</t>
         </is>
       </c>
       <c r="F73" s="5" t="n">
@@ -3471,10 +3471,10 @@
         <v>166</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K73" s="8" t="n">
-        <v>1896</v>
+        <v>2768</v>
       </c>
     </row>
     <row r="74" ht="19" customHeight="1">
@@ -3488,11 +3488,11 @@
         <v>1.01</v>
       </c>
       <c r="D74" s="8" t="n">
-        <v>140000</v>
+        <v>131000</v>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>140k</t>
+          <t>131k</t>
         </is>
       </c>
       <c r="F74" s="5" t="n">
@@ -3508,10 +3508,10 @@
         <v>169</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K74" s="8" t="n">
-        <v>1934</v>
+        <v>2822</v>
       </c>
     </row>
     <row r="75" ht="19" customHeight="1">
@@ -3522,14 +3522,14 @@
         <v>111</v>
       </c>
       <c r="C75" s="6" t="n">
-        <v>1.0143</v>
+        <v>1.01</v>
       </c>
       <c r="D75" s="8" t="n">
-        <v>142000</v>
+        <v>131001</v>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>142k</t>
+          <t>131k</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
@@ -3545,10 +3545,10 @@
         <v>172</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K75" s="8" t="n">
-        <v>1972</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="76" ht="19" customHeight="1">
@@ -3559,14 +3559,14 @@
         <v>112.5</v>
       </c>
       <c r="C76" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0153</v>
       </c>
       <c r="D76" s="8" t="n">
-        <v>143000</v>
+        <v>133000</v>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>143k</t>
+          <t>133k</t>
         </is>
       </c>
       <c r="F76" s="5" t="n">
@@ -3582,10 +3582,10 @@
         <v>175</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K76" s="8" t="n">
-        <v>2010</v>
+        <v>2930</v>
       </c>
     </row>
     <row r="77" ht="19" customHeight="1">
@@ -3596,14 +3596,14 @@
         <v>114</v>
       </c>
       <c r="C77" s="6" t="n">
-        <v>1.01</v>
+        <v>1.015</v>
       </c>
       <c r="D77" s="8" t="n">
-        <v>143001</v>
+        <v>135000</v>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>143k</t>
+          <t>135k</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
@@ -3619,10 +3619,10 @@
         <v>178</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K77" s="8" t="n">
-        <v>2048</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="78" ht="19" customHeight="1">
@@ -3636,11 +3636,11 @@
         <v>1.01</v>
       </c>
       <c r="D78" s="8" t="n">
-        <v>144000</v>
+        <v>136000</v>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>144k</t>
+          <t>136k</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
@@ -3656,10 +3656,10 @@
         <v>181</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K78" s="8" t="n">
-        <v>2086</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="79" ht="19" customHeight="1">
@@ -3670,14 +3670,14 @@
         <v>117</v>
       </c>
       <c r="C79" s="6" t="n">
-        <v>1.0139</v>
+        <v>1.0147</v>
       </c>
       <c r="D79" s="8" t="n">
-        <v>146000</v>
+        <v>138000</v>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>146k</t>
+          <t>138k</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
@@ -3693,10 +3693,10 @@
         <v>184</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K79" s="8" t="n">
-        <v>2124</v>
+        <v>3092</v>
       </c>
     </row>
     <row r="80" ht="19" customHeight="1">
@@ -3707,14 +3707,14 @@
         <v>118.5</v>
       </c>
       <c r="C80" s="6" t="n">
-        <v>1.0137</v>
+        <v>1.0145</v>
       </c>
       <c r="D80" s="8" t="n">
-        <v>148000</v>
+        <v>140000</v>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>148k</t>
+          <t>140k</t>
         </is>
       </c>
       <c r="F80" s="5" t="n">
@@ -3730,10 +3730,10 @@
         <v>187</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K80" s="8" t="n">
-        <v>2162</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="81" ht="19" customHeight="1">
@@ -3747,11 +3747,11 @@
         <v>1.01</v>
       </c>
       <c r="D81" s="8" t="n">
-        <v>149000</v>
+        <v>141000</v>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>149k</t>
+          <t>141k</t>
         </is>
       </c>
       <c r="F81" s="5" t="n">
@@ -3767,10 +3767,10 @@
         <v>190</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K81" s="8" t="n">
-        <v>2200</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="82" ht="19" customHeight="1">
@@ -3781,14 +3781,14 @@
         <v>121.5</v>
       </c>
       <c r="C82" s="6" t="n">
-        <v>1.0134</v>
+        <v>1.0142</v>
       </c>
       <c r="D82" s="8" t="n">
-        <v>151000</v>
+        <v>143000</v>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>151k</t>
+          <t>143k</t>
         </is>
       </c>
       <c r="F82" s="5" t="n">
@@ -3804,10 +3804,10 @@
         <v>193</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K82" s="8" t="n">
-        <v>2241</v>
+        <v>3258</v>
       </c>
     </row>
     <row r="83" ht="19" customHeight="1">
@@ -3818,14 +3818,14 @@
         <v>123</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>1.0199</v>
+        <v>1.028</v>
       </c>
       <c r="D83" s="8" t="n">
-        <v>154000</v>
+        <v>147000</v>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>154k</t>
+          <t>147k</t>
         </is>
       </c>
       <c r="F83" s="5" t="n">
@@ -3841,10 +3841,10 @@
         <v>196</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K83" s="8" t="n">
-        <v>2282</v>
+        <v>3316</v>
       </c>
     </row>
     <row r="84" ht="19" customHeight="1">
@@ -3855,14 +3855,14 @@
         <v>124.5</v>
       </c>
       <c r="C84" s="6" t="n">
-        <v>1.026</v>
+        <v>1.0408</v>
       </c>
       <c r="D84" s="8" t="n">
-        <v>158000</v>
+        <v>153000</v>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>158k</t>
+          <t>153k</t>
         </is>
       </c>
       <c r="F84" s="5" t="n">
@@ -3878,10 +3878,10 @@
         <v>199</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K84" s="8" t="n">
-        <v>2323</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="85" ht="19" customHeight="1">
@@ -3892,14 +3892,14 @@
         <v>126</v>
       </c>
       <c r="C85" s="6" t="n">
-        <v>1.0127</v>
+        <v>1.0131</v>
       </c>
       <c r="D85" s="8" t="n">
-        <v>160000</v>
+        <v>155000</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>160k</t>
+          <t>155k</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
@@ -3915,10 +3915,10 @@
         <v>202</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K85" s="8" t="n">
-        <v>2364</v>
+        <v>3432</v>
       </c>
     </row>
     <row r="86" ht="19" customHeight="1">
@@ -3929,14 +3929,14 @@
         <v>127.5</v>
       </c>
       <c r="C86" s="6" t="n">
-        <v>1.025</v>
+        <v>1.0194</v>
       </c>
       <c r="D86" s="8" t="n">
-        <v>164000</v>
+        <v>158000</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>164k</t>
+          <t>158k</t>
         </is>
       </c>
       <c r="F86" s="5" t="n">
@@ -3952,10 +3952,10 @@
         <v>205</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K86" s="8" t="n">
-        <v>2405</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="87" ht="19" customHeight="1">
@@ -3969,11 +3969,11 @@
         <v>1.01</v>
       </c>
       <c r="D87" s="8" t="n">
-        <v>165000</v>
+        <v>158001</v>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>165k</t>
+          <t>158k</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
@@ -3989,10 +3989,10 @@
         <v>208</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K87" s="8" t="n">
-        <v>2446</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="88" ht="19" customHeight="1">
@@ -4006,11 +4006,11 @@
         <v>1.01</v>
       </c>
       <c r="D88" s="8" t="n">
-        <v>165001</v>
+        <v>159000</v>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>165k</t>
+          <t>159k</t>
         </is>
       </c>
       <c r="F88" s="5" t="n">
@@ -4026,10 +4026,10 @@
         <v>211</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K88" s="8" t="n">
-        <v>2487</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="89" ht="19" customHeight="1">
@@ -4043,11 +4043,11 @@
         <v>1.01</v>
       </c>
       <c r="D89" s="8" t="n">
-        <v>166000</v>
+        <v>159001</v>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>166k</t>
+          <t>159k</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
@@ -4063,10 +4063,10 @@
         <v>214</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K89" s="8" t="n">
-        <v>2528</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="90" ht="19" customHeight="1">
@@ -4080,11 +4080,11 @@
         <v>1.01</v>
       </c>
       <c r="D90" s="8" t="n">
-        <v>167000</v>
+        <v>160000</v>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>167k</t>
+          <t>160k</t>
         </is>
       </c>
       <c r="F90" s="5" t="n">
@@ -4100,10 +4100,10 @@
         <v>217</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K90" s="8" t="n">
-        <v>2569</v>
+        <v>3722</v>
       </c>
     </row>
     <row r="91" ht="19" customHeight="1">
@@ -4114,14 +4114,14 @@
         <v>135</v>
       </c>
       <c r="C91" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0125</v>
       </c>
       <c r="D91" s="8" t="n">
-        <v>168000</v>
+        <v>162000</v>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>168k</t>
+          <t>162k</t>
         </is>
       </c>
       <c r="F91" s="5" t="n">
@@ -4137,10 +4137,10 @@
         <v>220</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="K91" s="8" t="n">
-        <v>2610</v>
+        <v>3780</v>
       </c>
     </row>
     <row r="92" ht="19" customHeight="1">
@@ -4151,14 +4151,14 @@
         <v>136.5</v>
       </c>
       <c r="C92" s="6" t="n">
-        <v>1.0179</v>
+        <v>1.0185</v>
       </c>
       <c r="D92" s="8" t="n">
-        <v>171000</v>
+        <v>165000</v>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>171k</t>
+          <t>165k</t>
         </is>
       </c>
       <c r="F92" s="5" t="n">
@@ -4174,10 +4174,10 @@
         <v>223</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K92" s="8" t="n">
-        <v>2654</v>
+        <v>3842</v>
       </c>
     </row>
     <row r="93" ht="19" customHeight="1">
@@ -4188,14 +4188,14 @@
         <v>138</v>
       </c>
       <c r="C93" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0121</v>
       </c>
       <c r="D93" s="8" t="n">
-        <v>172000</v>
+        <v>167000</v>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>172k</t>
+          <t>167k</t>
         </is>
       </c>
       <c r="F93" s="5" t="n">
@@ -4211,10 +4211,10 @@
         <v>226</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K93" s="8" t="n">
-        <v>2698</v>
+        <v>3904</v>
       </c>
     </row>
     <row r="94" ht="19" customHeight="1">
@@ -4225,14 +4225,14 @@
         <v>139.5</v>
       </c>
       <c r="C94" s="6" t="n">
-        <v>1.0174</v>
+        <v>1.012</v>
       </c>
       <c r="D94" s="8" t="n">
-        <v>175000</v>
+        <v>169000</v>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>175k</t>
+          <t>169k</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
@@ -4248,10 +4248,10 @@
         <v>229</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K94" s="8" t="n">
-        <v>2742</v>
+        <v>3966</v>
       </c>
     </row>
     <row r="95" ht="19" customHeight="1">
@@ -4262,14 +4262,14 @@
         <v>141</v>
       </c>
       <c r="C95" s="6" t="n">
-        <v>1.0114</v>
+        <v>1.01</v>
       </c>
       <c r="D95" s="8" t="n">
-        <v>177000</v>
+        <v>170000</v>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>177k</t>
+          <t>170k</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
@@ -4285,10 +4285,10 @@
         <v>232</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K95" s="8" t="n">
-        <v>2786</v>
+        <v>4028</v>
       </c>
     </row>
     <row r="96" ht="19" customHeight="1">
@@ -4299,14 +4299,14 @@
         <v>142.5</v>
       </c>
       <c r="C96" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0118</v>
       </c>
       <c r="D96" s="8" t="n">
-        <v>178000</v>
+        <v>172000</v>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>178k</t>
+          <t>172k</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
@@ -4322,10 +4322,10 @@
         <v>235</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K96" s="8" t="n">
-        <v>2830</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="97" ht="19" customHeight="1">
@@ -4336,14 +4336,14 @@
         <v>144</v>
       </c>
       <c r="C97" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0116</v>
       </c>
       <c r="D97" s="8" t="n">
-        <v>179000</v>
+        <v>174000</v>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>179k</t>
+          <t>174k</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
@@ -4359,10 +4359,10 @@
         <v>238</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K97" s="8" t="n">
-        <v>2874</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="98" ht="19" customHeight="1">
@@ -4373,14 +4373,14 @@
         <v>145.5</v>
       </c>
       <c r="C98" s="6" t="n">
-        <v>1.0112</v>
+        <v>1.0115</v>
       </c>
       <c r="D98" s="8" t="n">
-        <v>181000</v>
+        <v>176000</v>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>181k</t>
+          <t>176k</t>
         </is>
       </c>
       <c r="F98" s="5" t="n">
@@ -4396,10 +4396,10 @@
         <v>241</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K98" s="8" t="n">
-        <v>2918</v>
+        <v>4214</v>
       </c>
     </row>
     <row r="99" ht="19" customHeight="1">
@@ -4410,14 +4410,14 @@
         <v>147</v>
       </c>
       <c r="C99" s="6" t="n">
-        <v>1.0221</v>
+        <v>1.0284</v>
       </c>
       <c r="D99" s="8" t="n">
-        <v>185000</v>
+        <v>181000</v>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>185k</t>
+          <t>181k</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
@@ -4433,10 +4433,10 @@
         <v>244</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K99" s="8" t="n">
-        <v>2962</v>
+        <v>4276</v>
       </c>
     </row>
     <row r="100" ht="19" customHeight="1">
@@ -4447,14 +4447,14 @@
         <v>148.5</v>
       </c>
       <c r="C100" s="6" t="n">
-        <v>1.027</v>
+        <v>1.0276</v>
       </c>
       <c r="D100" s="8" t="n">
-        <v>190000</v>
+        <v>186000</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>190k</t>
+          <t>186k</t>
         </is>
       </c>
       <c r="F100" s="5" t="n">
@@ -4470,10 +4470,10 @@
         <v>247</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K100" s="8" t="n">
-        <v>3006</v>
+        <v>4338</v>
       </c>
     </row>
     <row r="101" ht="19" customHeight="1">
@@ -4484,14 +4484,14 @@
         <v>150</v>
       </c>
       <c r="C101" s="6" t="n">
-        <v>1.0105</v>
+        <v>1.0108</v>
       </c>
       <c r="D101" s="8" t="n">
-        <v>192000</v>
+        <v>188000</v>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>192k</t>
+          <t>188k</t>
         </is>
       </c>
       <c r="F101" s="5" t="n">
@@ -4507,10 +4507,10 @@
         <v>250</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K101" s="8" t="n">
-        <v>3050</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="102" ht="19" customHeight="1">
@@ -4521,14 +4521,14 @@
         <v>151.5</v>
       </c>
       <c r="C102" s="6" t="n">
-        <v>1.0104</v>
+        <v>1.0106</v>
       </c>
       <c r="D102" s="8" t="n">
-        <v>194000</v>
+        <v>190000</v>
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>194k</t>
+          <t>190k</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
@@ -4544,10 +4544,10 @@
         <v>253</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K102" s="8" t="n">
-        <v>3097</v>
+        <v>4466</v>
       </c>
     </row>
     <row r="103" ht="19" customHeight="1">
@@ -4558,14 +4558,14 @@
         <v>153</v>
       </c>
       <c r="C103" s="6" t="n">
-        <v>1.0103</v>
+        <v>1.0158</v>
       </c>
       <c r="D103" s="8" t="n">
-        <v>196000</v>
+        <v>193000</v>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>196k</t>
+          <t>193k</t>
         </is>
       </c>
       <c r="F103" s="5" t="n">
@@ -4581,10 +4581,10 @@
         <v>256</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K103" s="8" t="n">
-        <v>3144</v>
+        <v>4532</v>
       </c>
     </row>
     <row r="104" ht="19" customHeight="1">
@@ -4595,14 +4595,14 @@
         <v>154.5</v>
       </c>
       <c r="C104" s="6" t="n">
-        <v>1.0102</v>
+        <v>1.0104</v>
       </c>
       <c r="D104" s="8" t="n">
-        <v>198000</v>
+        <v>195000</v>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>198k</t>
+          <t>195k</t>
         </is>
       </c>
       <c r="F104" s="5" t="n">
@@ -4618,10 +4618,10 @@
         <v>259</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K104" s="8" t="n">
-        <v>3191</v>
+        <v>4598</v>
       </c>
     </row>
     <row r="105" ht="19" customHeight="1">
@@ -4632,14 +4632,14 @@
         <v>156</v>
       </c>
       <c r="C105" s="6" t="n">
-        <v>1.0101</v>
+        <v>1.0103</v>
       </c>
       <c r="D105" s="8" t="n">
-        <v>200000</v>
+        <v>197000</v>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>200k</t>
+          <t>197k</t>
         </is>
       </c>
       <c r="F105" s="5" t="n">
@@ -4655,10 +4655,10 @@
         <v>262</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K105" s="8" t="n">
-        <v>3238</v>
+        <v>4664</v>
       </c>
     </row>
     <row r="106" ht="19" customHeight="1">
@@ -4669,14 +4669,14 @@
         <v>157.5</v>
       </c>
       <c r="C106" s="6" t="n">
-        <v>1.015</v>
+        <v>1.0152</v>
       </c>
       <c r="D106" s="8" t="n">
-        <v>203000</v>
+        <v>200000</v>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>203k</t>
+          <t>200k</t>
         </is>
       </c>
       <c r="F106" s="5" t="n">
@@ -4692,10 +4692,10 @@
         <v>265</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K106" s="8" t="n">
-        <v>3285</v>
+        <v>4730</v>
       </c>
     </row>
     <row r="107" ht="19" customHeight="1">
@@ -4709,11 +4709,11 @@
         <v>1.01</v>
       </c>
       <c r="D107" s="8" t="n">
-        <v>205000</v>
+        <v>202000</v>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>205k</t>
+          <t>202k</t>
         </is>
       </c>
       <c r="F107" s="5" t="n">
@@ -4729,10 +4729,10 @@
         <v>268</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K107" s="8" t="n">
-        <v>3332</v>
+        <v>4796</v>
       </c>
     </row>
     <row r="108" ht="19" customHeight="1">
@@ -4746,11 +4746,11 @@
         <v>1.01</v>
       </c>
       <c r="D108" s="8" t="n">
-        <v>207000</v>
+        <v>204000</v>
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>207k</t>
+          <t>204k</t>
         </is>
       </c>
       <c r="F108" s="5" t="n">
@@ -4766,10 +4766,10 @@
         <v>271</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K108" s="8" t="n">
-        <v>3379</v>
+        <v>4862</v>
       </c>
     </row>
     <row r="109" ht="19" customHeight="1">
@@ -4780,14 +4780,14 @@
         <v>162</v>
       </c>
       <c r="C109" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0147</v>
       </c>
       <c r="D109" s="8" t="n">
-        <v>209000</v>
+        <v>207000</v>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>209k</t>
+          <t>207k</t>
         </is>
       </c>
       <c r="F109" s="5" t="n">
@@ -4803,10 +4803,10 @@
         <v>274</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K109" s="8" t="n">
-        <v>3426</v>
+        <v>4928</v>
       </c>
     </row>
     <row r="110" ht="19" customHeight="1">
@@ -4820,11 +4820,11 @@
         <v>1.01</v>
       </c>
       <c r="D110" s="8" t="n">
-        <v>211000</v>
+        <v>209000</v>
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>211k</t>
+          <t>209k</t>
         </is>
       </c>
       <c r="F110" s="5" t="n">
@@ -4840,10 +4840,10 @@
         <v>277</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K110" s="8" t="n">
-        <v>3473</v>
+        <v>4994</v>
       </c>
     </row>
     <row r="111" ht="19" customHeight="1">
@@ -4857,11 +4857,11 @@
         <v>1.01</v>
       </c>
       <c r="D111" s="8" t="n">
-        <v>213000</v>
+        <v>211000</v>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>213k</t>
+          <t>211k</t>
         </is>
       </c>
       <c r="F111" s="5" t="n">
@@ -4877,10 +4877,10 @@
         <v>280</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="K111" s="8" t="n">
-        <v>3520</v>
+        <v>5060</v>
       </c>
     </row>
     <row r="112" ht="19" customHeight="1">
@@ -4891,14 +4891,14 @@
         <v>166.5</v>
       </c>
       <c r="C112" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0142</v>
       </c>
       <c r="D112" s="8" t="n">
-        <v>215000</v>
+        <v>214000</v>
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>215k</t>
+          <t>214k</t>
         </is>
       </c>
       <c r="F112" s="5" t="n">
@@ -4914,10 +4914,10 @@
         <v>283</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K112" s="8" t="n">
-        <v>3570</v>
+        <v>5130</v>
       </c>
     </row>
     <row r="113" ht="19" customHeight="1">
@@ -4928,14 +4928,14 @@
         <v>168</v>
       </c>
       <c r="C113" s="6" t="n">
-        <v>1.014</v>
+        <v>1.01</v>
       </c>
       <c r="D113" s="8" t="n">
-        <v>218000</v>
+        <v>216000</v>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>218k</t>
+          <t>216k</t>
         </is>
       </c>
       <c r="F113" s="5" t="n">
@@ -4951,10 +4951,10 @@
         <v>286</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K113" s="8" t="n">
-        <v>3620</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="114" ht="19" customHeight="1">
@@ -4968,11 +4968,11 @@
         <v>1.01</v>
       </c>
       <c r="D114" s="8" t="n">
-        <v>220000</v>
+        <v>218000</v>
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>220k</t>
+          <t>218k</t>
         </is>
       </c>
       <c r="F114" s="5" t="n">
@@ -4988,10 +4988,10 @@
         <v>289</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K114" s="8" t="n">
-        <v>3670</v>
+        <v>5270</v>
       </c>
     </row>
     <row r="115" ht="19" customHeight="1">
@@ -5002,14 +5002,14 @@
         <v>171</v>
       </c>
       <c r="C115" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0138</v>
       </c>
       <c r="D115" s="8" t="n">
-        <v>222000</v>
+        <v>221000</v>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>222k</t>
+          <t>221k</t>
         </is>
       </c>
       <c r="F115" s="5" t="n">
@@ -5025,10 +5025,10 @@
         <v>292</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K115" s="8" t="n">
-        <v>3720</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="116" ht="19" customHeight="1">
@@ -5042,11 +5042,11 @@
         <v>1.01</v>
       </c>
       <c r="D116" s="8" t="n">
-        <v>224000</v>
+        <v>223000</v>
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>224k</t>
+          <t>223k</t>
         </is>
       </c>
       <c r="F116" s="5" t="n">
@@ -5062,10 +5062,10 @@
         <v>295</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K116" s="8" t="n">
-        <v>3770</v>
+        <v>5410</v>
       </c>
     </row>
     <row r="117" ht="19" customHeight="1">
@@ -5079,11 +5079,11 @@
         <v>1.01</v>
       </c>
       <c r="D117" s="8" t="n">
-        <v>226000</v>
+        <v>225000</v>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>226k</t>
+          <t>225k</t>
         </is>
       </c>
       <c r="F117" s="5" t="n">
@@ -5099,10 +5099,10 @@
         <v>298</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K117" s="8" t="n">
-        <v>3820</v>
+        <v>5480</v>
       </c>
     </row>
     <row r="118" ht="19" customHeight="1">
@@ -5113,7 +5113,7 @@
         <v>175.5</v>
       </c>
       <c r="C118" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0133</v>
       </c>
       <c r="D118" s="8" t="n">
         <v>228000</v>
@@ -5136,10 +5136,10 @@
         <v>301</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K118" s="8" t="n">
-        <v>3870</v>
+        <v>5550</v>
       </c>
     </row>
     <row r="119" ht="19" customHeight="1">
@@ -5173,10 +5173,10 @@
         <v>304</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K119" s="8" t="n">
-        <v>3920</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
@@ -5210,10 +5210,10 @@
         <v>307</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K120" s="8" t="n">
-        <v>3970</v>
+        <v>5690</v>
       </c>
     </row>
     <row r="121" ht="19" customHeight="1">
@@ -5247,10 +5247,10 @@
         <v>310</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="K121" s="8" t="n">
-        <v>4020</v>
+        <v>5760</v>
       </c>
     </row>
     <row r="122" ht="19" customHeight="1">
@@ -5284,10 +5284,10 @@
         <v>313</v>
       </c>
       <c r="J122" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K122" s="8" t="n">
-        <v>4073</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="123" ht="19" customHeight="1">
@@ -5321,10 +5321,10 @@
         <v>316</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K123" s="8" t="n">
-        <v>4126</v>
+        <v>5908</v>
       </c>
     </row>
     <row r="124" ht="19" customHeight="1">
@@ -5335,14 +5335,14 @@
         <v>184.5</v>
       </c>
       <c r="C124" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0126</v>
       </c>
       <c r="D124" s="8" t="n">
-        <v>241000</v>
+        <v>242000</v>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>241k</t>
+          <t>242k</t>
         </is>
       </c>
       <c r="F124" s="5" t="n">
@@ -5358,10 +5358,10 @@
         <v>319</v>
       </c>
       <c r="J124" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K124" s="8" t="n">
-        <v>4179</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="125" ht="19" customHeight="1">
@@ -5375,11 +5375,11 @@
         <v>1.01</v>
       </c>
       <c r="D125" s="8" t="n">
-        <v>243000</v>
+        <v>244000</v>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>243k</t>
+          <t>244k</t>
         </is>
       </c>
       <c r="F125" s="5" t="n">
@@ -5395,10 +5395,10 @@
         <v>322</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K125" s="8" t="n">
-        <v>4232</v>
+        <v>6056</v>
       </c>
     </row>
     <row r="126" ht="19" customHeight="1">
@@ -5412,11 +5412,11 @@
         <v>1.01</v>
       </c>
       <c r="D126" s="8" t="n">
-        <v>245000</v>
+        <v>246000</v>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>245k</t>
+          <t>246k</t>
         </is>
       </c>
       <c r="F126" s="5" t="n">
@@ -5432,10 +5432,10 @@
         <v>325</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K126" s="8" t="n">
-        <v>4285</v>
+        <v>6130</v>
       </c>
     </row>
     <row r="127" ht="19" customHeight="1">
@@ -5446,14 +5446,14 @@
         <v>189</v>
       </c>
       <c r="C127" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0122</v>
       </c>
       <c r="D127" s="8" t="n">
-        <v>247000</v>
+        <v>249000</v>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>247k</t>
+          <t>249k</t>
         </is>
       </c>
       <c r="F127" s="5" t="n">
@@ -5469,10 +5469,10 @@
         <v>328</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K127" s="8" t="n">
-        <v>4338</v>
+        <v>6204</v>
       </c>
     </row>
     <row r="128" ht="19" customHeight="1">
@@ -5483,14 +5483,14 @@
         <v>190.5</v>
       </c>
       <c r="C128" s="6" t="n">
-        <v>1.0121</v>
+        <v>1.01</v>
       </c>
       <c r="D128" s="8" t="n">
-        <v>250000</v>
+        <v>251000</v>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>250k</t>
+          <t>251k</t>
         </is>
       </c>
       <c r="F128" s="5" t="n">
@@ -5506,10 +5506,10 @@
         <v>331</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K128" s="8" t="n">
-        <v>4391</v>
+        <v>6278</v>
       </c>
     </row>
     <row r="129" ht="19" customHeight="1">
@@ -5523,11 +5523,11 @@
         <v>1.01</v>
       </c>
       <c r="D129" s="8" t="n">
-        <v>252000</v>
+        <v>253000</v>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>252k</t>
+          <t>253k</t>
         </is>
       </c>
       <c r="F129" s="5" t="n">
@@ -5543,10 +5543,10 @@
         <v>334</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K129" s="8" t="n">
-        <v>4444</v>
+        <v>6352</v>
       </c>
     </row>
     <row r="130" ht="19" customHeight="1">
@@ -5557,14 +5557,14 @@
         <v>193.5</v>
       </c>
       <c r="C130" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0119</v>
       </c>
       <c r="D130" s="8" t="n">
-        <v>254000</v>
+        <v>256000</v>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>254k</t>
+          <t>256k</t>
         </is>
       </c>
       <c r="F130" s="5" t="n">
@@ -5580,10 +5580,10 @@
         <v>337</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K130" s="8" t="n">
-        <v>4497</v>
+        <v>6426</v>
       </c>
     </row>
     <row r="131" ht="19" customHeight="1">
@@ -5597,11 +5597,11 @@
         <v>1.01</v>
       </c>
       <c r="D131" s="8" t="n">
-        <v>256000</v>
+        <v>258000</v>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>256k</t>
+          <t>258k</t>
         </is>
       </c>
       <c r="F131" s="5" t="n">
@@ -5617,10 +5617,10 @@
         <v>340</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K131" s="8" t="n">
-        <v>4550</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="132" ht="19" customHeight="1">
@@ -5634,11 +5634,11 @@
         <v>1.01</v>
       </c>
       <c r="D132" s="8" t="n">
-        <v>258000</v>
+        <v>260000</v>
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>258k</t>
+          <t>260k</t>
         </is>
       </c>
       <c r="F132" s="5" t="n">
@@ -5654,10 +5654,10 @@
         <v>343</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K132" s="8" t="n">
-        <v>4606</v>
+        <v>6578</v>
       </c>
     </row>
     <row r="133" ht="19" customHeight="1">
@@ -5668,14 +5668,14 @@
         <v>198</v>
       </c>
       <c r="C133" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0115</v>
       </c>
       <c r="D133" s="8" t="n">
-        <v>260000</v>
+        <v>263000</v>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>260k</t>
+          <t>263k</t>
         </is>
       </c>
       <c r="F133" s="5" t="n">
@@ -5691,10 +5691,10 @@
         <v>346</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K133" s="8" t="n">
-        <v>4662</v>
+        <v>6656</v>
       </c>
     </row>
     <row r="134" ht="19" customHeight="1">
@@ -5708,11 +5708,11 @@
         <v>1.01</v>
       </c>
       <c r="D134" s="8" t="n">
-        <v>262000</v>
+        <v>265000</v>
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>262k</t>
+          <t>265k</t>
         </is>
       </c>
       <c r="F134" s="5" t="n">
@@ -5728,10 +5728,10 @@
         <v>349</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K134" s="8" t="n">
-        <v>4718</v>
+        <v>6734</v>
       </c>
     </row>
     <row r="135" ht="19" customHeight="1">
@@ -5745,11 +5745,11 @@
         <v>1.01</v>
       </c>
       <c r="D135" s="8" t="n">
-        <v>264000</v>
+        <v>267000</v>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>264k</t>
+          <t>267k</t>
         </is>
       </c>
       <c r="F135" s="5" t="n">
@@ -5765,10 +5765,10 @@
         <v>352</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K135" s="8" t="n">
-        <v>4774</v>
+        <v>6812</v>
       </c>
     </row>
     <row r="136" ht="19" customHeight="1">
@@ -5779,14 +5779,14 @@
         <v>202.5</v>
       </c>
       <c r="C136" s="6" t="n">
-        <v>1.0114</v>
+        <v>1.0112</v>
       </c>
       <c r="D136" s="8" t="n">
-        <v>267000</v>
+        <v>270000</v>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>267k</t>
+          <t>270k</t>
         </is>
       </c>
       <c r="F136" s="5" t="n">
@@ -5802,10 +5802,10 @@
         <v>355</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K136" s="8" t="n">
-        <v>4830</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="137" ht="19" customHeight="1">
@@ -5819,11 +5819,11 @@
         <v>1.01</v>
       </c>
       <c r="D137" s="8" t="n">
-        <v>269000</v>
+        <v>272000</v>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>269k</t>
+          <t>272k</t>
         </is>
       </c>
       <c r="F137" s="5" t="n">
@@ -5839,10 +5839,10 @@
         <v>358</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K137" s="8" t="n">
-        <v>4886</v>
+        <v>6968</v>
       </c>
     </row>
     <row r="138" ht="19" customHeight="1">
@@ -5856,11 +5856,11 @@
         <v>1.01</v>
       </c>
       <c r="D138" s="8" t="n">
-        <v>271000</v>
+        <v>274000</v>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>271k</t>
+          <t>274k</t>
         </is>
       </c>
       <c r="F138" s="5" t="n">
@@ -5876,10 +5876,10 @@
         <v>361</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K138" s="8" t="n">
-        <v>4942</v>
+        <v>7046</v>
       </c>
     </row>
     <row r="139" ht="19" customHeight="1">
@@ -5890,14 +5890,14 @@
         <v>207</v>
       </c>
       <c r="C139" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0109</v>
       </c>
       <c r="D139" s="8" t="n">
-        <v>273000</v>
+        <v>277000</v>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>273k</t>
+          <t>277k</t>
         </is>
       </c>
       <c r="F139" s="5" t="n">
@@ -5913,10 +5913,10 @@
         <v>364</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K139" s="8" t="n">
-        <v>4998</v>
+        <v>7124</v>
       </c>
     </row>
     <row r="140" ht="19" customHeight="1">
@@ -5930,11 +5930,11 @@
         <v>1.01</v>
       </c>
       <c r="D140" s="8" t="n">
-        <v>275000</v>
+        <v>279000</v>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>275k</t>
+          <t>279k</t>
         </is>
       </c>
       <c r="F140" s="5" t="n">
@@ -5950,10 +5950,10 @@
         <v>367</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K140" s="8" t="n">
-        <v>5054</v>
+        <v>7202</v>
       </c>
     </row>
     <row r="141" ht="19" customHeight="1">
@@ -5967,11 +5967,11 @@
         <v>1.01</v>
       </c>
       <c r="D141" s="8" t="n">
-        <v>277000</v>
+        <v>281000</v>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>277k</t>
+          <t>281k</t>
         </is>
       </c>
       <c r="F141" s="5" t="n">
@@ -5987,10 +5987,10 @@
         <v>370</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="K141" s="8" t="n">
-        <v>5110</v>
+        <v>7280</v>
       </c>
     </row>
     <row r="142" ht="19" customHeight="1">
@@ -6001,14 +6001,14 @@
         <v>211.5</v>
       </c>
       <c r="C142" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0107</v>
       </c>
       <c r="D142" s="8" t="n">
-        <v>279000</v>
+        <v>284000</v>
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>279k</t>
+          <t>284k</t>
         </is>
       </c>
       <c r="F142" s="5" t="n">
@@ -6024,10 +6024,10 @@
         <v>373</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K142" s="8" t="n">
-        <v>5169</v>
+        <v>7362</v>
       </c>
     </row>
     <row r="143" ht="19" customHeight="1">
@@ -6038,14 +6038,14 @@
         <v>213</v>
       </c>
       <c r="C143" s="6" t="n">
-        <v>1.0108</v>
+        <v>1.01</v>
       </c>
       <c r="D143" s="8" t="n">
-        <v>282000</v>
+        <v>286000</v>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>282k</t>
+          <t>286k</t>
         </is>
       </c>
       <c r="F143" s="5" t="n">
@@ -6061,10 +6061,10 @@
         <v>376</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K143" s="8" t="n">
-        <v>5228</v>
+        <v>7444</v>
       </c>
     </row>
     <row r="144" ht="19" customHeight="1">
@@ -6078,11 +6078,11 @@
         <v>1.01</v>
       </c>
       <c r="D144" s="8" t="n">
-        <v>284000</v>
+        <v>288000</v>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>284k</t>
+          <t>288k</t>
         </is>
       </c>
       <c r="F144" s="5" t="n">
@@ -6098,10 +6098,10 @@
         <v>379</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K144" s="8" t="n">
-        <v>5287</v>
+        <v>7526</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1">
@@ -6112,14 +6112,14 @@
         <v>216</v>
       </c>
       <c r="C145" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0104</v>
       </c>
       <c r="D145" s="8" t="n">
-        <v>286000</v>
+        <v>291000</v>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>286k</t>
+          <t>291k</t>
         </is>
       </c>
       <c r="F145" s="5" t="n">
@@ -6135,10 +6135,10 @@
         <v>382</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K145" s="8" t="n">
-        <v>5346</v>
+        <v>7608</v>
       </c>
     </row>
     <row r="146" ht="19" customHeight="1">
@@ -6152,11 +6152,11 @@
         <v>1.01</v>
       </c>
       <c r="D146" s="8" t="n">
-        <v>288000</v>
+        <v>293000</v>
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>288k</t>
+          <t>293k</t>
         </is>
       </c>
       <c r="F146" s="5" t="n">
@@ -6172,10 +6172,10 @@
         <v>385</v>
       </c>
       <c r="J146" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K146" s="8" t="n">
-        <v>5405</v>
+        <v>7690</v>
       </c>
     </row>
     <row r="147" ht="19" customHeight="1">
@@ -6189,11 +6189,11 @@
         <v>1.01</v>
       </c>
       <c r="D147" s="8" t="n">
-        <v>290000</v>
+        <v>295000</v>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>290k</t>
+          <t>295k</t>
         </is>
       </c>
       <c r="F147" s="5" t="n">
@@ -6209,10 +6209,10 @@
         <v>388</v>
       </c>
       <c r="J147" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K147" s="8" t="n">
-        <v>5464</v>
+        <v>7772</v>
       </c>
     </row>
     <row r="148" ht="19" customHeight="1">
@@ -6223,14 +6223,14 @@
         <v>220.5</v>
       </c>
       <c r="C148" s="6" t="n">
-        <v>1.01</v>
+        <v>1.0102</v>
       </c>
       <c r="D148" s="8" t="n">
-        <v>292000</v>
+        <v>298000</v>
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>292k</t>
+          <t>298k</t>
         </is>
       </c>
       <c r="F148" s="5" t="n">
@@ -6246,10 +6246,10 @@
         <v>391</v>
       </c>
       <c r="J148" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K148" s="8" t="n">
-        <v>5523</v>
+        <v>7854</v>
       </c>
     </row>
     <row r="149" ht="19" customHeight="1">
@@ -6263,11 +6263,11 @@
         <v>1.01</v>
       </c>
       <c r="D149" s="8" t="n">
-        <v>294000</v>
+        <v>300000</v>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>294k</t>
+          <t>300k</t>
         </is>
       </c>
       <c r="F149" s="5" t="n">
@@ -6283,10 +6283,10 @@
         <v>394</v>
       </c>
       <c r="J149" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K149" s="8" t="n">
-        <v>5582</v>
+        <v>7936</v>
       </c>
     </row>
     <row r="150" ht="19" customHeight="1">
@@ -6297,14 +6297,14 @@
         <v>223.5</v>
       </c>
       <c r="C150" s="6" t="n">
-        <v>1.0102</v>
+        <v>1.01</v>
       </c>
       <c r="D150" s="8" t="n">
-        <v>297000</v>
+        <v>302000</v>
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>297k</t>
+          <t>302k</t>
         </is>
       </c>
       <c r="F150" s="5" t="n">
@@ -6320,10 +6320,10 @@
         <v>397</v>
       </c>
       <c r="J150" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K150" s="8" t="n">
-        <v>5641</v>
+        <v>8018</v>
       </c>
     </row>
     <row r="151" ht="19" customHeight="1">
@@ -6337,11 +6337,11 @@
         <v>1.01</v>
       </c>
       <c r="D151" s="8" t="n">
-        <v>299000</v>
+        <v>305000</v>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>299k</t>
+          <t>305k</t>
         </is>
       </c>
       <c r="F151" s="5" t="n">
@@ -6357,10 +6357,10 @@
         <v>400</v>
       </c>
       <c r="J151" s="5" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="K151" s="8" t="n">
-        <v>5700</v>
+        <v>8100</v>
       </c>
     </row>
   </sheetData>
